--- a/out/thesis/tables/warnings.xlsx
+++ b/out/thesis/tables/warnings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="16">
   <si>
     <t>category</t>
   </si>
@@ -31,13 +31,31 @@
     <t>completion_intraday_unavailable</t>
   </si>
   <si>
+    <t>model_fallback</t>
+  </si>
+  <si>
     <t>missing_completion_coverage</t>
+  </si>
+  <si>
+    <t>regression_skipped</t>
   </si>
   <si>
     <t>Completion intraday metrics left missing because no dedicated completion intraday panel was uploaded</t>
   </si>
   <si>
+    <t>Using market_adjusted (OLS market model not estimated: insufficient obs or zero benchmark variance)</t>
+  </si>
+  <si>
+    <t>Using mean_adjusted (benchmark sparse or estimation window short)</t>
+  </si>
+  <si>
     <t>No daily panel contains the completion date for re-anchored completion analysis</t>
+  </si>
+  <si>
+    <t>announcement_bhar: no usable predictors</t>
+  </si>
+  <si>
+    <t>completion_bhar: no usable predictors</t>
   </si>
   <si>
     <t>intraday</t>
@@ -375,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D515"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -397,10 +415,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -411,13 +429,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -425,13 +440,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -439,13 +451,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -453,13 +462,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -467,13 +473,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
         <v>9</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -481,13 +484,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -495,13 +495,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
         <v>9</v>
       </c>
       <c r="D9">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -509,13 +506,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -523,13 +517,10 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -537,13 +528,10 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -551,13 +539,10 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
         <v>9</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -565,9 +550,6 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14">
@@ -579,13 +561,10 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -593,13 +572,10 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
         <v>9</v>
       </c>
       <c r="D16">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -607,13 +583,10 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s">
         <v>9</v>
       </c>
       <c r="D17">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -621,13 +594,10 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -635,13 +605,10 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -649,13 +616,10 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -663,13 +627,10 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -677,13 +638,10 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -691,13 +649,10 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>69</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -705,13 +660,10 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -719,13 +671,10 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -733,13 +682,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -747,13 +693,10 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -761,13 +704,10 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>87</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -775,13 +715,10 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -789,13 +726,10 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>89</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -803,13 +737,10 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -817,13 +748,10 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -831,13 +759,10 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>98</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -845,13 +770,10 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -859,13 +781,10 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35">
-        <v>103</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -873,13 +792,10 @@
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>104</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -887,13 +803,10 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>105</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -901,13 +814,10 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -915,13 +825,10 @@
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39">
-        <v>107</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -929,13 +836,10 @@
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>108</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -943,13 +847,10 @@
         <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41">
-        <v>110</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -957,13 +858,10 @@
         <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42">
-        <v>113</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -971,13 +869,10 @@
         <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43">
-        <v>114</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -985,13 +880,10 @@
         <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44">
-        <v>122</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -999,13 +891,10 @@
         <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>124</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1013,13 +902,10 @@
         <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1027,13 +913,10 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47">
-        <v>126</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1041,13 +924,10 @@
         <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D48">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1055,13 +935,10 @@
         <v>5</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D49">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1069,13 +946,10 @@
         <v>5</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D50">
-        <v>129</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1083,13 +957,10 @@
         <v>5</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D51">
-        <v>133</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1097,13 +968,10 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D52">
-        <v>137</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1111,13 +979,10 @@
         <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D53">
-        <v>141</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1125,13 +990,10 @@
         <v>5</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D54">
-        <v>156</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1139,13 +1001,10 @@
         <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D55">
-        <v>158</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1153,13 +1012,10 @@
         <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D56">
-        <v>159</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1167,13 +1023,10 @@
         <v>5</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D57">
-        <v>160</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1181,13 +1034,10 @@
         <v>5</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D58">
-        <v>165</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1195,13 +1045,10 @@
         <v>5</v>
       </c>
       <c r="B59" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D59">
-        <v>166</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1209,13 +1056,10 @@
         <v>5</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D60">
-        <v>168</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1223,13 +1067,10 @@
         <v>5</v>
       </c>
       <c r="B61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D61">
-        <v>173</v>
+        <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1237,13 +1078,10 @@
         <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D62">
-        <v>179</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1251,13 +1089,10 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D63">
-        <v>180</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1265,13 +1100,10 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D64">
-        <v>190</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1279,13 +1111,10 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D65">
-        <v>195</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1293,13 +1122,10 @@
         <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D66">
-        <v>196</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1307,13 +1133,5136 @@
         <v>5</v>
       </c>
       <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>5</v>
+      </c>
+      <c r="B85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>5</v>
+      </c>
+      <c r="B99" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>5</v>
+      </c>
+      <c r="B104" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>5</v>
+      </c>
+      <c r="B105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>5</v>
+      </c>
+      <c r="B107" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>5</v>
+      </c>
+      <c r="B108" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>5</v>
+      </c>
+      <c r="B109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>5</v>
+      </c>
+      <c r="B110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>5</v>
+      </c>
+      <c r="B113" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>5</v>
+      </c>
+      <c r="B114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>5</v>
+      </c>
+      <c r="B115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>5</v>
+      </c>
+      <c r="B116" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>5</v>
+      </c>
+      <c r="B118" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>5</v>
+      </c>
+      <c r="B119" t="s">
+        <v>10</v>
+      </c>
+      <c r="D119">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>5</v>
+      </c>
+      <c r="B120" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
+        <v>5</v>
+      </c>
+      <c r="B121" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
+        <v>5</v>
+      </c>
+      <c r="B122" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>5</v>
+      </c>
+      <c r="B123" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>5</v>
+      </c>
+      <c r="B124" t="s">
+        <v>9</v>
+      </c>
+      <c r="D124">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>5</v>
+      </c>
+      <c r="B125" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>5</v>
+      </c>
+      <c r="B126" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>5</v>
+      </c>
+      <c r="B127" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>5</v>
+      </c>
+      <c r="B128" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>5</v>
+      </c>
+      <c r="B129" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>5</v>
+      </c>
+      <c r="B130" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>5</v>
+      </c>
+      <c r="B132" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>5</v>
+      </c>
+      <c r="B133" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>5</v>
+      </c>
+      <c r="B134" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
+        <v>5</v>
+      </c>
+      <c r="B135" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
+        <v>5</v>
+      </c>
+      <c r="B136" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
+        <v>5</v>
+      </c>
+      <c r="B137" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
+        <v>5</v>
+      </c>
+      <c r="B138" t="s">
+        <v>10</v>
+      </c>
+      <c r="D138">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139" t="s">
+        <v>10</v>
+      </c>
+      <c r="D139">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
+        <v>5</v>
+      </c>
+      <c r="B140" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>5</v>
+      </c>
+      <c r="B141" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
+        <v>5</v>
+      </c>
+      <c r="B142" t="s">
+        <v>10</v>
+      </c>
+      <c r="D142">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
+        <v>5</v>
+      </c>
+      <c r="B143" t="s">
+        <v>10</v>
+      </c>
+      <c r="D143">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" t="s">
+        <v>5</v>
+      </c>
+      <c r="B144" t="s">
+        <v>10</v>
+      </c>
+      <c r="D144">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" t="s">
+        <v>5</v>
+      </c>
+      <c r="B145" t="s">
+        <v>10</v>
+      </c>
+      <c r="D145">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" t="s">
+        <v>5</v>
+      </c>
+      <c r="B146" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" t="s">
+        <v>5</v>
+      </c>
+      <c r="B147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D147">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148" t="s">
+        <v>10</v>
+      </c>
+      <c r="D148">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" t="s">
+        <v>5</v>
+      </c>
+      <c r="B149" t="s">
+        <v>10</v>
+      </c>
+      <c r="D149">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" t="s">
+        <v>5</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="D150">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" t="s">
+        <v>5</v>
+      </c>
+      <c r="B151" t="s">
+        <v>10</v>
+      </c>
+      <c r="D151">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" t="s">
+        <v>5</v>
+      </c>
+      <c r="B152" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" t="s">
+        <v>5</v>
+      </c>
+      <c r="B153" t="s">
+        <v>10</v>
+      </c>
+      <c r="D153">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" t="s">
+        <v>5</v>
+      </c>
+      <c r="B154" t="s">
+        <v>10</v>
+      </c>
+      <c r="D154">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" t="s">
+        <v>5</v>
+      </c>
+      <c r="B155" t="s">
+        <v>10</v>
+      </c>
+      <c r="D155">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" t="s">
+        <v>5</v>
+      </c>
+      <c r="B156" t="s">
+        <v>10</v>
+      </c>
+      <c r="D156">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" t="s">
+        <v>5</v>
+      </c>
+      <c r="B157" t="s">
+        <v>10</v>
+      </c>
+      <c r="D157">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" t="s">
+        <v>5</v>
+      </c>
+      <c r="B158" t="s">
+        <v>10</v>
+      </c>
+      <c r="D158">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" t="s">
+        <v>5</v>
+      </c>
+      <c r="B159" t="s">
+        <v>10</v>
+      </c>
+      <c r="D159">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" t="s">
+        <v>5</v>
+      </c>
+      <c r="B160" t="s">
+        <v>10</v>
+      </c>
+      <c r="D160">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
+        <v>5</v>
+      </c>
+      <c r="B161" t="s">
+        <v>10</v>
+      </c>
+      <c r="D161">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
+        <v>5</v>
+      </c>
+      <c r="B162" t="s">
+        <v>10</v>
+      </c>
+      <c r="D162">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" t="s">
+        <v>10</v>
+      </c>
+      <c r="D163">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
+        <v>5</v>
+      </c>
+      <c r="B164" t="s">
+        <v>10</v>
+      </c>
+      <c r="D164">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
+        <v>5</v>
+      </c>
+      <c r="B165" t="s">
+        <v>10</v>
+      </c>
+      <c r="D165">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" t="s">
+        <v>5</v>
+      </c>
+      <c r="B166" t="s">
+        <v>10</v>
+      </c>
+      <c r="D166">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
+        <v>5</v>
+      </c>
+      <c r="B167" t="s">
+        <v>10</v>
+      </c>
+      <c r="D167">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
+        <v>5</v>
+      </c>
+      <c r="B168" t="s">
+        <v>10</v>
+      </c>
+      <c r="D168">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" t="s">
+        <v>5</v>
+      </c>
+      <c r="B169" t="s">
+        <v>10</v>
+      </c>
+      <c r="D169">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" t="s">
+        <v>5</v>
+      </c>
+      <c r="B170" t="s">
+        <v>10</v>
+      </c>
+      <c r="D170">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" t="s">
+        <v>5</v>
+      </c>
+      <c r="B171" t="s">
+        <v>10</v>
+      </c>
+      <c r="D171">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" t="s">
+        <v>5</v>
+      </c>
+      <c r="B172" t="s">
+        <v>10</v>
+      </c>
+      <c r="D172">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" t="s">
+        <v>5</v>
+      </c>
+      <c r="B173" t="s">
+        <v>10</v>
+      </c>
+      <c r="D173">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" t="s">
+        <v>5</v>
+      </c>
+      <c r="B174" t="s">
+        <v>10</v>
+      </c>
+      <c r="D174">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" t="s">
+        <v>5</v>
+      </c>
+      <c r="B175" t="s">
+        <v>10</v>
+      </c>
+      <c r="D175">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" t="s">
+        <v>5</v>
+      </c>
+      <c r="B176" t="s">
+        <v>10</v>
+      </c>
+      <c r="D176">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" t="s">
+        <v>5</v>
+      </c>
+      <c r="B177" t="s">
+        <v>10</v>
+      </c>
+      <c r="D177">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" t="s">
+        <v>5</v>
+      </c>
+      <c r="B178" t="s">
+        <v>10</v>
+      </c>
+      <c r="D178">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" t="s">
+        <v>5</v>
+      </c>
+      <c r="B179" t="s">
+        <v>10</v>
+      </c>
+      <c r="D179">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" t="s">
+        <v>5</v>
+      </c>
+      <c r="B180" t="s">
+        <v>10</v>
+      </c>
+      <c r="D180">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" t="s">
+        <v>5</v>
+      </c>
+      <c r="B181" t="s">
+        <v>10</v>
+      </c>
+      <c r="D181">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" t="s">
+        <v>5</v>
+      </c>
+      <c r="B182" t="s">
+        <v>10</v>
+      </c>
+      <c r="D182">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
+        <v>5</v>
+      </c>
+      <c r="B183" t="s">
+        <v>10</v>
+      </c>
+      <c r="D183">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
+        <v>5</v>
+      </c>
+      <c r="B184" t="s">
+        <v>10</v>
+      </c>
+      <c r="D184">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
+        <v>5</v>
+      </c>
+      <c r="B185" t="s">
+        <v>10</v>
+      </c>
+      <c r="D185">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" t="s">
+        <v>5</v>
+      </c>
+      <c r="B186" t="s">
+        <v>10</v>
+      </c>
+      <c r="D186">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" t="s">
+        <v>5</v>
+      </c>
+      <c r="B187" t="s">
+        <v>10</v>
+      </c>
+      <c r="D187">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" t="s">
+        <v>5</v>
+      </c>
+      <c r="B188" t="s">
+        <v>10</v>
+      </c>
+      <c r="D188">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" t="s">
+        <v>5</v>
+      </c>
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+      <c r="D189">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
+        <v>5</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="D190">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
+        <v>5</v>
+      </c>
+      <c r="B191" t="s">
+        <v>10</v>
+      </c>
+      <c r="D191">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" t="s">
+        <v>5</v>
+      </c>
+      <c r="B192" t="s">
+        <v>10</v>
+      </c>
+      <c r="D192">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" t="s">
+        <v>5</v>
+      </c>
+      <c r="B193" t="s">
+        <v>10</v>
+      </c>
+      <c r="D193">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" t="s">
+        <v>5</v>
+      </c>
+      <c r="B194" t="s">
+        <v>10</v>
+      </c>
+      <c r="D194">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" t="s">
+        <v>5</v>
+      </c>
+      <c r="B195" t="s">
+        <v>10</v>
+      </c>
+      <c r="D195">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" t="s">
+        <v>5</v>
+      </c>
+      <c r="B196" t="s">
+        <v>10</v>
+      </c>
+      <c r="D196">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" t="s">
+        <v>5</v>
+      </c>
+      <c r="B197" t="s">
+        <v>10</v>
+      </c>
+      <c r="D197">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" t="s">
+        <v>5</v>
+      </c>
+      <c r="B198" t="s">
+        <v>10</v>
+      </c>
+      <c r="D198">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" t="s">
+        <v>5</v>
+      </c>
+      <c r="B199" t="s">
+        <v>10</v>
+      </c>
+      <c r="D199">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" t="s">
+        <v>5</v>
+      </c>
+      <c r="B200" t="s">
+        <v>10</v>
+      </c>
+      <c r="D200">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" t="s">
+        <v>5</v>
+      </c>
+      <c r="B201" t="s">
+        <v>10</v>
+      </c>
+      <c r="D201">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" t="s">
+        <v>5</v>
+      </c>
+      <c r="B202" t="s">
+        <v>10</v>
+      </c>
+      <c r="D202">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" t="s">
+        <v>5</v>
+      </c>
+      <c r="B203" t="s">
+        <v>10</v>
+      </c>
+      <c r="D203">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" t="s">
+        <v>5</v>
+      </c>
+      <c r="B204" t="s">
+        <v>10</v>
+      </c>
+      <c r="D204">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" t="s">
+        <v>5</v>
+      </c>
+      <c r="B205" t="s">
+        <v>10</v>
+      </c>
+      <c r="D205">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
+        <v>5</v>
+      </c>
+      <c r="B206" t="s">
+        <v>10</v>
+      </c>
+      <c r="D206">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" t="s">
+        <v>5</v>
+      </c>
+      <c r="B207" t="s">
+        <v>10</v>
+      </c>
+      <c r="D207">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" t="s">
+        <v>5</v>
+      </c>
+      <c r="B208" t="s">
+        <v>10</v>
+      </c>
+      <c r="D208">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" t="s">
+        <v>5</v>
+      </c>
+      <c r="B209" t="s">
+        <v>10</v>
+      </c>
+      <c r="D209">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" t="s">
+        <v>5</v>
+      </c>
+      <c r="B210" t="s">
+        <v>10</v>
+      </c>
+      <c r="D210">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" t="s">
+        <v>5</v>
+      </c>
+      <c r="B211" t="s">
+        <v>10</v>
+      </c>
+      <c r="D211">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" t="s">
+        <v>5</v>
+      </c>
+      <c r="B212" t="s">
+        <v>10</v>
+      </c>
+      <c r="D212">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" t="s">
+        <v>5</v>
+      </c>
+      <c r="B213" t="s">
+        <v>10</v>
+      </c>
+      <c r="D213">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" t="s">
+        <v>5</v>
+      </c>
+      <c r="B214" t="s">
+        <v>10</v>
+      </c>
+      <c r="D214">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" t="s">
+        <v>5</v>
+      </c>
+      <c r="B215" t="s">
+        <v>10</v>
+      </c>
+      <c r="D215">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" t="s">
+        <v>5</v>
+      </c>
+      <c r="B216" t="s">
+        <v>10</v>
+      </c>
+      <c r="D216">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" t="s">
+        <v>5</v>
+      </c>
+      <c r="B217" t="s">
+        <v>10</v>
+      </c>
+      <c r="D217">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" t="s">
+        <v>5</v>
+      </c>
+      <c r="B218" t="s">
+        <v>10</v>
+      </c>
+      <c r="D218">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" t="s">
+        <v>5</v>
+      </c>
+      <c r="B219" t="s">
+        <v>10</v>
+      </c>
+      <c r="D219">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" t="s">
+        <v>5</v>
+      </c>
+      <c r="B220" t="s">
+        <v>10</v>
+      </c>
+      <c r="D220">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" t="s">
+        <v>5</v>
+      </c>
+      <c r="B221" t="s">
+        <v>10</v>
+      </c>
+      <c r="D221">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" t="s">
+        <v>5</v>
+      </c>
+      <c r="B222" t="s">
+        <v>10</v>
+      </c>
+      <c r="D222">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" t="s">
+        <v>5</v>
+      </c>
+      <c r="B223" t="s">
+        <v>10</v>
+      </c>
+      <c r="D223">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" t="s">
+        <v>5</v>
+      </c>
+      <c r="B224" t="s">
+        <v>10</v>
+      </c>
+      <c r="D224">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" t="s">
+        <v>5</v>
+      </c>
+      <c r="B225" t="s">
+        <v>10</v>
+      </c>
+      <c r="D225">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
+        <v>5</v>
+      </c>
+      <c r="B226" t="s">
+        <v>10</v>
+      </c>
+      <c r="D226">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
+        <v>5</v>
+      </c>
+      <c r="B227" t="s">
+        <v>10</v>
+      </c>
+      <c r="D227">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
+        <v>5</v>
+      </c>
+      <c r="B228" t="s">
+        <v>10</v>
+      </c>
+      <c r="D228">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
+        <v>5</v>
+      </c>
+      <c r="B229" t="s">
+        <v>10</v>
+      </c>
+      <c r="D229">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
+        <v>5</v>
+      </c>
+      <c r="B230" t="s">
+        <v>10</v>
+      </c>
+      <c r="D230">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>5</v>
+      </c>
+      <c r="B231" t="s">
+        <v>10</v>
+      </c>
+      <c r="D231">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>5</v>
+      </c>
+      <c r="B232" t="s">
+        <v>10</v>
+      </c>
+      <c r="D232">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>5</v>
+      </c>
+      <c r="B233" t="s">
+        <v>10</v>
+      </c>
+      <c r="D233">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>5</v>
+      </c>
+      <c r="B234" t="s">
+        <v>10</v>
+      </c>
+      <c r="D234">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>5</v>
+      </c>
+      <c r="B235" t="s">
+        <v>10</v>
+      </c>
+      <c r="D235">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>5</v>
+      </c>
+      <c r="B236" t="s">
+        <v>10</v>
+      </c>
+      <c r="D236">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>5</v>
+      </c>
+      <c r="B237" t="s">
+        <v>10</v>
+      </c>
+      <c r="D237">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>5</v>
+      </c>
+      <c r="B238" t="s">
+        <v>10</v>
+      </c>
+      <c r="D238">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>5</v>
+      </c>
+      <c r="B239" t="s">
+        <v>10</v>
+      </c>
+      <c r="D239">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>5</v>
+      </c>
+      <c r="B240" t="s">
+        <v>10</v>
+      </c>
+      <c r="D240">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>5</v>
+      </c>
+      <c r="B241" t="s">
+        <v>10</v>
+      </c>
+      <c r="D241">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>5</v>
+      </c>
+      <c r="B242" t="s">
+        <v>10</v>
+      </c>
+      <c r="D242">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>5</v>
+      </c>
+      <c r="B243" t="s">
+        <v>9</v>
+      </c>
+      <c r="D243">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>5</v>
+      </c>
+      <c r="B244" t="s">
+        <v>10</v>
+      </c>
+      <c r="D244">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>5</v>
+      </c>
+      <c r="B245" t="s">
+        <v>9</v>
+      </c>
+      <c r="D245">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
+        <v>5</v>
+      </c>
+      <c r="B246" t="s">
+        <v>10</v>
+      </c>
+      <c r="D246">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>5</v>
+      </c>
+      <c r="B247" t="s">
+        <v>9</v>
+      </c>
+      <c r="D247">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
+        <v>5</v>
+      </c>
+      <c r="B248" t="s">
+        <v>9</v>
+      </c>
+      <c r="D248">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" t="s">
+        <v>5</v>
+      </c>
+      <c r="B249" t="s">
+        <v>9</v>
+      </c>
+      <c r="D249">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" t="s">
+        <v>5</v>
+      </c>
+      <c r="B250" t="s">
+        <v>9</v>
+      </c>
+      <c r="D250">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" t="s">
+        <v>5</v>
+      </c>
+      <c r="B251" t="s">
+        <v>9</v>
+      </c>
+      <c r="D251">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
+        <v>5</v>
+      </c>
+      <c r="B252" t="s">
+        <v>9</v>
+      </c>
+      <c r="D252">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
+        <v>5</v>
+      </c>
+      <c r="B253" t="s">
+        <v>10</v>
+      </c>
+      <c r="D253">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
+        <v>5</v>
+      </c>
+      <c r="B254" t="s">
+        <v>9</v>
+      </c>
+      <c r="D254">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
+        <v>5</v>
+      </c>
+      <c r="B255" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
+        <v>5</v>
+      </c>
+      <c r="B256" t="s">
+        <v>10</v>
+      </c>
+      <c r="D256">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" t="s">
+        <v>5</v>
+      </c>
+      <c r="B257" t="s">
+        <v>9</v>
+      </c>
+      <c r="D257">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" t="s">
+        <v>5</v>
+      </c>
+      <c r="B258" t="s">
+        <v>9</v>
+      </c>
+      <c r="D258">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" t="s">
+        <v>5</v>
+      </c>
+      <c r="B259" t="s">
+        <v>10</v>
+      </c>
+      <c r="D259">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" t="s">
+        <v>5</v>
+      </c>
+      <c r="B260" t="s">
+        <v>10</v>
+      </c>
+      <c r="D260">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" t="s">
+        <v>5</v>
+      </c>
+      <c r="B261" t="s">
+        <v>10</v>
+      </c>
+      <c r="D261">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" t="s">
+        <v>5</v>
+      </c>
+      <c r="B262" t="s">
+        <v>10</v>
+      </c>
+      <c r="D262">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" t="s">
+        <v>5</v>
+      </c>
+      <c r="B263" t="s">
+        <v>10</v>
+      </c>
+      <c r="D263">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" t="s">
+        <v>5</v>
+      </c>
+      <c r="B264" t="s">
+        <v>10</v>
+      </c>
+      <c r="D264">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" t="s">
+        <v>5</v>
+      </c>
+      <c r="B265" t="s">
+        <v>10</v>
+      </c>
+      <c r="D265">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" t="s">
+        <v>5</v>
+      </c>
+      <c r="B266" t="s">
+        <v>10</v>
+      </c>
+      <c r="D266">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" t="s">
+        <v>5</v>
+      </c>
+      <c r="B267" t="s">
+        <v>10</v>
+      </c>
+      <c r="D267">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" t="s">
+        <v>5</v>
+      </c>
+      <c r="B268" t="s">
+        <v>10</v>
+      </c>
+      <c r="D268">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" t="s">
+        <v>5</v>
+      </c>
+      <c r="B269" t="s">
+        <v>10</v>
+      </c>
+      <c r="D269">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" t="s">
+        <v>5</v>
+      </c>
+      <c r="B270" t="s">
+        <v>10</v>
+      </c>
+      <c r="D270">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" t="s">
+        <v>5</v>
+      </c>
+      <c r="B271" t="s">
+        <v>10</v>
+      </c>
+      <c r="D271">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" t="s">
+        <v>5</v>
+      </c>
+      <c r="B272" t="s">
+        <v>10</v>
+      </c>
+      <c r="D272">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" t="s">
+        <v>5</v>
+      </c>
+      <c r="B273" t="s">
+        <v>10</v>
+      </c>
+      <c r="D273">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" t="s">
+        <v>5</v>
+      </c>
+      <c r="B274" t="s">
+        <v>10</v>
+      </c>
+      <c r="D274">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" t="s">
+        <v>5</v>
+      </c>
+      <c r="B275" t="s">
+        <v>10</v>
+      </c>
+      <c r="D275">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" t="s">
+        <v>5</v>
+      </c>
+      <c r="B276" t="s">
+        <v>10</v>
+      </c>
+      <c r="D276">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" t="s">
+        <v>5</v>
+      </c>
+      <c r="B277" t="s">
+        <v>10</v>
+      </c>
+      <c r="D277">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" t="s">
+        <v>5</v>
+      </c>
+      <c r="B278" t="s">
+        <v>10</v>
+      </c>
+      <c r="D278">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" t="s">
+        <v>5</v>
+      </c>
+      <c r="B279" t="s">
+        <v>10</v>
+      </c>
+      <c r="D279">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" t="s">
+        <v>5</v>
+      </c>
+      <c r="B280" t="s">
+        <v>10</v>
+      </c>
+      <c r="D280">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" t="s">
+        <v>5</v>
+      </c>
+      <c r="B281" t="s">
+        <v>10</v>
+      </c>
+      <c r="D281">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" t="s">
+        <v>5</v>
+      </c>
+      <c r="B282" t="s">
+        <v>10</v>
+      </c>
+      <c r="D282">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" t="s">
+        <v>5</v>
+      </c>
+      <c r="B283" t="s">
+        <v>10</v>
+      </c>
+      <c r="D283">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" t="s">
+        <v>5</v>
+      </c>
+      <c r="B284" t="s">
+        <v>10</v>
+      </c>
+      <c r="D284">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" t="s">
+        <v>5</v>
+      </c>
+      <c r="B285" t="s">
+        <v>10</v>
+      </c>
+      <c r="D285">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" t="s">
+        <v>5</v>
+      </c>
+      <c r="B286" t="s">
+        <v>10</v>
+      </c>
+      <c r="D286">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" t="s">
+        <v>5</v>
+      </c>
+      <c r="B287" t="s">
+        <v>10</v>
+      </c>
+      <c r="D287">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" t="s">
+        <v>5</v>
+      </c>
+      <c r="B288" t="s">
+        <v>10</v>
+      </c>
+      <c r="D288">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" t="s">
+        <v>5</v>
+      </c>
+      <c r="B289" t="s">
+        <v>10</v>
+      </c>
+      <c r="D289">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" t="s">
+        <v>5</v>
+      </c>
+      <c r="B290" t="s">
+        <v>10</v>
+      </c>
+      <c r="D290">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" t="s">
+        <v>5</v>
+      </c>
+      <c r="B291" t="s">
+        <v>10</v>
+      </c>
+      <c r="D291">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" t="s">
+        <v>5</v>
+      </c>
+      <c r="B292" t="s">
+        <v>10</v>
+      </c>
+      <c r="D292">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" t="s">
+        <v>5</v>
+      </c>
+      <c r="B293" t="s">
+        <v>10</v>
+      </c>
+      <c r="D293">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" t="s">
+        <v>5</v>
+      </c>
+      <c r="B294" t="s">
+        <v>10</v>
+      </c>
+      <c r="D294">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" t="s">
+        <v>5</v>
+      </c>
+      <c r="B295" t="s">
+        <v>10</v>
+      </c>
+      <c r="D295">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" t="s">
+        <v>5</v>
+      </c>
+      <c r="B296" t="s">
+        <v>10</v>
+      </c>
+      <c r="D296">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" t="s">
+        <v>5</v>
+      </c>
+      <c r="B297" t="s">
+        <v>10</v>
+      </c>
+      <c r="D297">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" t="s">
+        <v>5</v>
+      </c>
+      <c r="B298" t="s">
+        <v>10</v>
+      </c>
+      <c r="D298">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" t="s">
+        <v>5</v>
+      </c>
+      <c r="B299" t="s">
+        <v>10</v>
+      </c>
+      <c r="D299">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" t="s">
+        <v>5</v>
+      </c>
+      <c r="B300" t="s">
+        <v>10</v>
+      </c>
+      <c r="D300">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" t="s">
+        <v>5</v>
+      </c>
+      <c r="B301" t="s">
+        <v>10</v>
+      </c>
+      <c r="D301">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" t="s">
+        <v>5</v>
+      </c>
+      <c r="B302" t="s">
+        <v>10</v>
+      </c>
+      <c r="D302">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" t="s">
+        <v>5</v>
+      </c>
+      <c r="B303" t="s">
+        <v>10</v>
+      </c>
+      <c r="D303">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" t="s">
+        <v>5</v>
+      </c>
+      <c r="B304" t="s">
+        <v>10</v>
+      </c>
+      <c r="D304">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" t="s">
+        <v>5</v>
+      </c>
+      <c r="B305" t="s">
+        <v>10</v>
+      </c>
+      <c r="D305">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" t="s">
+        <v>5</v>
+      </c>
+      <c r="B306" t="s">
+        <v>10</v>
+      </c>
+      <c r="D306">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" t="s">
+        <v>5</v>
+      </c>
+      <c r="B307" t="s">
+        <v>10</v>
+      </c>
+      <c r="D307">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" t="s">
+        <v>5</v>
+      </c>
+      <c r="B308" t="s">
+        <v>10</v>
+      </c>
+      <c r="D308">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" t="s">
+        <v>5</v>
+      </c>
+      <c r="B309" t="s">
+        <v>10</v>
+      </c>
+      <c r="D309">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" t="s">
+        <v>5</v>
+      </c>
+      <c r="B310" t="s">
+        <v>10</v>
+      </c>
+      <c r="D310">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" t="s">
+        <v>5</v>
+      </c>
+      <c r="B311" t="s">
+        <v>10</v>
+      </c>
+      <c r="D311">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" t="s">
+        <v>5</v>
+      </c>
+      <c r="B312" t="s">
+        <v>10</v>
+      </c>
+      <c r="D312">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" t="s">
+        <v>5</v>
+      </c>
+      <c r="B313" t="s">
+        <v>10</v>
+      </c>
+      <c r="D313">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" t="s">
+        <v>5</v>
+      </c>
+      <c r="B314" t="s">
+        <v>10</v>
+      </c>
+      <c r="D314">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" t="s">
+        <v>5</v>
+      </c>
+      <c r="B315" t="s">
+        <v>10</v>
+      </c>
+      <c r="D315">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" t="s">
+        <v>5</v>
+      </c>
+      <c r="B316" t="s">
+        <v>10</v>
+      </c>
+      <c r="D316">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" t="s">
+        <v>5</v>
+      </c>
+      <c r="B317" t="s">
+        <v>10</v>
+      </c>
+      <c r="D317">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" t="s">
+        <v>5</v>
+      </c>
+      <c r="B318" t="s">
+        <v>10</v>
+      </c>
+      <c r="D318">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" t="s">
+        <v>5</v>
+      </c>
+      <c r="B319" t="s">
+        <v>10</v>
+      </c>
+      <c r="D319">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" t="s">
+        <v>5</v>
+      </c>
+      <c r="B320" t="s">
+        <v>10</v>
+      </c>
+      <c r="D320">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" t="s">
+        <v>5</v>
+      </c>
+      <c r="B321" t="s">
+        <v>10</v>
+      </c>
+      <c r="D321">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" t="s">
+        <v>5</v>
+      </c>
+      <c r="B322" t="s">
+        <v>10</v>
+      </c>
+      <c r="D322">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" t="s">
+        <v>5</v>
+      </c>
+      <c r="B323" t="s">
+        <v>10</v>
+      </c>
+      <c r="D323">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" t="s">
+        <v>5</v>
+      </c>
+      <c r="B324" t="s">
+        <v>10</v>
+      </c>
+      <c r="D324">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" t="s">
+        <v>5</v>
+      </c>
+      <c r="B325" t="s">
+        <v>10</v>
+      </c>
+      <c r="D325">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" t="s">
+        <v>5</v>
+      </c>
+      <c r="B326" t="s">
+        <v>10</v>
+      </c>
+      <c r="D326">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" t="s">
+        <v>5</v>
+      </c>
+      <c r="B327" t="s">
+        <v>10</v>
+      </c>
+      <c r="D327">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" t="s">
+        <v>5</v>
+      </c>
+      <c r="B328" t="s">
+        <v>10</v>
+      </c>
+      <c r="D328">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" t="s">
+        <v>5</v>
+      </c>
+      <c r="B329" t="s">
+        <v>10</v>
+      </c>
+      <c r="D329">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" t="s">
+        <v>5</v>
+      </c>
+      <c r="B330" t="s">
+        <v>10</v>
+      </c>
+      <c r="D330">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" t="s">
+        <v>5</v>
+      </c>
+      <c r="B331" t="s">
+        <v>10</v>
+      </c>
+      <c r="D331">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" t="s">
+        <v>5</v>
+      </c>
+      <c r="B332" t="s">
+        <v>10</v>
+      </c>
+      <c r="D332">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" t="s">
+        <v>5</v>
+      </c>
+      <c r="B333" t="s">
+        <v>10</v>
+      </c>
+      <c r="D333">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" t="s">
+        <v>5</v>
+      </c>
+      <c r="B334" t="s">
+        <v>10</v>
+      </c>
+      <c r="D334">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" t="s">
+        <v>5</v>
+      </c>
+      <c r="B335" t="s">
+        <v>10</v>
+      </c>
+      <c r="D335">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" t="s">
+        <v>5</v>
+      </c>
+      <c r="B336" t="s">
+        <v>10</v>
+      </c>
+      <c r="D336">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" t="s">
+        <v>5</v>
+      </c>
+      <c r="B337" t="s">
+        <v>10</v>
+      </c>
+      <c r="D337">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" t="s">
+        <v>5</v>
+      </c>
+      <c r="B338" t="s">
+        <v>10</v>
+      </c>
+      <c r="D338">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" t="s">
+        <v>5</v>
+      </c>
+      <c r="B339" t="s">
+        <v>10</v>
+      </c>
+      <c r="D339">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" t="s">
+        <v>5</v>
+      </c>
+      <c r="B340" t="s">
+        <v>10</v>
+      </c>
+      <c r="D340">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" t="s">
+        <v>5</v>
+      </c>
+      <c r="B341" t="s">
+        <v>10</v>
+      </c>
+      <c r="D341">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" t="s">
+        <v>5</v>
+      </c>
+      <c r="B342" t="s">
+        <v>10</v>
+      </c>
+      <c r="D342">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" t="s">
+        <v>5</v>
+      </c>
+      <c r="B343" t="s">
+        <v>10</v>
+      </c>
+      <c r="D343">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" t="s">
+        <v>5</v>
+      </c>
+      <c r="B344" t="s">
+        <v>10</v>
+      </c>
+      <c r="D344">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" t="s">
+        <v>5</v>
+      </c>
+      <c r="B345" t="s">
+        <v>10</v>
+      </c>
+      <c r="D345">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" t="s">
+        <v>5</v>
+      </c>
+      <c r="B346" t="s">
+        <v>10</v>
+      </c>
+      <c r="D346">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" t="s">
+        <v>5</v>
+      </c>
+      <c r="B347" t="s">
+        <v>10</v>
+      </c>
+      <c r="D347">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" t="s">
+        <v>5</v>
+      </c>
+      <c r="B348" t="s">
+        <v>10</v>
+      </c>
+      <c r="D348">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" t="s">
+        <v>5</v>
+      </c>
+      <c r="B349" t="s">
+        <v>10</v>
+      </c>
+      <c r="D349">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" t="s">
+        <v>5</v>
+      </c>
+      <c r="B350" t="s">
+        <v>10</v>
+      </c>
+      <c r="D350">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" t="s">
+        <v>5</v>
+      </c>
+      <c r="B351" t="s">
+        <v>10</v>
+      </c>
+      <c r="D351">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" t="s">
+        <v>5</v>
+      </c>
+      <c r="B352" t="s">
+        <v>10</v>
+      </c>
+      <c r="D352">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" t="s">
+        <v>5</v>
+      </c>
+      <c r="B353" t="s">
+        <v>10</v>
+      </c>
+      <c r="D353">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" t="s">
+        <v>5</v>
+      </c>
+      <c r="B354" t="s">
+        <v>10</v>
+      </c>
+      <c r="D354">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" t="s">
+        <v>5</v>
+      </c>
+      <c r="B355" t="s">
+        <v>10</v>
+      </c>
+      <c r="D355">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" t="s">
+        <v>5</v>
+      </c>
+      <c r="B356" t="s">
+        <v>10</v>
+      </c>
+      <c r="D356">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" t="s">
+        <v>5</v>
+      </c>
+      <c r="B357" t="s">
+        <v>10</v>
+      </c>
+      <c r="D357">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" t="s">
+        <v>5</v>
+      </c>
+      <c r="B358" t="s">
+        <v>10</v>
+      </c>
+      <c r="D358">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" t="s">
+        <v>5</v>
+      </c>
+      <c r="B359" t="s">
+        <v>10</v>
+      </c>
+      <c r="D359">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" t="s">
+        <v>5</v>
+      </c>
+      <c r="B360" t="s">
+        <v>10</v>
+      </c>
+      <c r="D360">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" t="s">
+        <v>5</v>
+      </c>
+      <c r="B361" t="s">
+        <v>10</v>
+      </c>
+      <c r="D361">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" t="s">
+        <v>5</v>
+      </c>
+      <c r="B362" t="s">
+        <v>10</v>
+      </c>
+      <c r="D362">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" t="s">
+        <v>5</v>
+      </c>
+      <c r="B363" t="s">
+        <v>10</v>
+      </c>
+      <c r="D363">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" t="s">
+        <v>5</v>
+      </c>
+      <c r="B364" t="s">
+        <v>10</v>
+      </c>
+      <c r="D364">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" t="s">
+        <v>11</v>
+      </c>
+      <c r="C365" t="s">
+        <v>15</v>
+      </c>
+      <c r="D365">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" t="s">
+        <v>6</v>
+      </c>
+      <c r="B366" t="s">
+        <v>11</v>
+      </c>
+      <c r="C366" t="s">
+        <v>15</v>
+      </c>
+      <c r="D366">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" t="s">
+        <v>6</v>
+      </c>
+      <c r="B367" t="s">
+        <v>11</v>
+      </c>
+      <c r="C367" t="s">
+        <v>15</v>
+      </c>
+      <c r="D367">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" t="s">
+        <v>6</v>
+      </c>
+      <c r="B368" t="s">
+        <v>11</v>
+      </c>
+      <c r="C368" t="s">
+        <v>15</v>
+      </c>
+      <c r="D368">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" t="s">
+        <v>6</v>
+      </c>
+      <c r="B369" t="s">
+        <v>11</v>
+      </c>
+      <c r="C369" t="s">
+        <v>15</v>
+      </c>
+      <c r="D369">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" t="s">
+        <v>6</v>
+      </c>
+      <c r="B370" t="s">
+        <v>11</v>
+      </c>
+      <c r="C370" t="s">
+        <v>15</v>
+      </c>
+      <c r="D370">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" t="s">
+        <v>6</v>
+      </c>
+      <c r="B371" t="s">
+        <v>11</v>
+      </c>
+      <c r="C371" t="s">
+        <v>15</v>
+      </c>
+      <c r="D371">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" t="s">
+        <v>5</v>
+      </c>
+      <c r="B372" t="s">
+        <v>9</v>
+      </c>
+      <c r="D372">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" t="s">
+        <v>11</v>
+      </c>
+      <c r="C373" t="s">
+        <v>15</v>
+      </c>
+      <c r="D373">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" t="s">
+        <v>5</v>
+      </c>
+      <c r="B374" t="s">
+        <v>9</v>
+      </c>
+      <c r="D374">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" t="s">
+        <v>6</v>
+      </c>
+      <c r="B375" t="s">
+        <v>11</v>
+      </c>
+      <c r="C375" t="s">
+        <v>15</v>
+      </c>
+      <c r="D375">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" t="s">
+        <v>6</v>
+      </c>
+      <c r="B376" t="s">
+        <v>11</v>
+      </c>
+      <c r="C376" t="s">
+        <v>15</v>
+      </c>
+      <c r="D376">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" t="s">
+        <v>6</v>
+      </c>
+      <c r="B377" t="s">
+        <v>11</v>
+      </c>
+      <c r="C377" t="s">
+        <v>15</v>
+      </c>
+      <c r="D377">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" t="s">
+        <v>5</v>
+      </c>
+      <c r="B378" t="s">
+        <v>9</v>
+      </c>
+      <c r="D378">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" t="s">
+        <v>6</v>
+      </c>
+      <c r="B379" t="s">
+        <v>11</v>
+      </c>
+      <c r="C379" t="s">
+        <v>15</v>
+      </c>
+      <c r="D379">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" t="s">
+        <v>5</v>
+      </c>
+      <c r="B380" t="s">
+        <v>10</v>
+      </c>
+      <c r="D380">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" t="s">
+        <v>5</v>
+      </c>
+      <c r="B381" t="s">
+        <v>9</v>
+      </c>
+      <c r="D381">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" t="s">
+        <v>6</v>
+      </c>
+      <c r="B382" t="s">
+        <v>11</v>
+      </c>
+      <c r="C382" t="s">
+        <v>15</v>
+      </c>
+      <c r="D382">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" t="s">
+        <v>5</v>
+      </c>
+      <c r="B383" t="s">
+        <v>10</v>
+      </c>
+      <c r="D383">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" t="s">
+        <v>6</v>
+      </c>
+      <c r="B384" t="s">
+        <v>11</v>
+      </c>
+      <c r="C384" t="s">
+        <v>15</v>
+      </c>
+      <c r="D384">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" t="s">
+        <v>6</v>
+      </c>
+      <c r="B385" t="s">
+        <v>11</v>
+      </c>
+      <c r="C385" t="s">
+        <v>15</v>
+      </c>
+      <c r="D385">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" t="s">
+        <v>5</v>
+      </c>
+      <c r="B386" t="s">
+        <v>10</v>
+      </c>
+      <c r="D386">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" t="s">
+        <v>5</v>
+      </c>
+      <c r="B387" t="s">
+        <v>10</v>
+      </c>
+      <c r="D387">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" t="s">
+        <v>5</v>
+      </c>
+      <c r="B388" t="s">
+        <v>10</v>
+      </c>
+      <c r="D388">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" t="s">
+        <v>5</v>
+      </c>
+      <c r="B389" t="s">
+        <v>10</v>
+      </c>
+      <c r="D389">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" t="s">
+        <v>11</v>
+      </c>
+      <c r="C390" t="s">
+        <v>15</v>
+      </c>
+      <c r="D390">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" t="s">
+        <v>5</v>
+      </c>
+      <c r="B391" t="s">
+        <v>10</v>
+      </c>
+      <c r="D391">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" t="s">
+        <v>5</v>
+      </c>
+      <c r="B392" t="s">
+        <v>10</v>
+      </c>
+      <c r="D392">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" t="s">
+        <v>6</v>
+      </c>
+      <c r="B393" t="s">
+        <v>11</v>
+      </c>
+      <c r="C393" t="s">
+        <v>15</v>
+      </c>
+      <c r="D393">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" t="s">
+        <v>6</v>
+      </c>
+      <c r="B394" t="s">
+        <v>11</v>
+      </c>
+      <c r="C394" t="s">
+        <v>15</v>
+      </c>
+      <c r="D394">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" t="s">
+        <v>5</v>
+      </c>
+      <c r="B395" t="s">
+        <v>10</v>
+      </c>
+      <c r="D395">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" t="s">
+        <v>5</v>
+      </c>
+      <c r="B396" t="s">
+        <v>10</v>
+      </c>
+      <c r="D396">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" t="s">
+        <v>5</v>
+      </c>
+      <c r="B397" t="s">
+        <v>10</v>
+      </c>
+      <c r="D397">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" t="s">
+        <v>5</v>
+      </c>
+      <c r="B398" t="s">
+        <v>10</v>
+      </c>
+      <c r="D398">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" t="s">
+        <v>5</v>
+      </c>
+      <c r="B399" t="s">
+        <v>10</v>
+      </c>
+      <c r="D399">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" t="s">
+        <v>6</v>
+      </c>
+      <c r="B400" t="s">
+        <v>11</v>
+      </c>
+      <c r="C400" t="s">
+        <v>15</v>
+      </c>
+      <c r="D400">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" t="s">
+        <v>6</v>
+      </c>
+      <c r="B401" t="s">
+        <v>11</v>
+      </c>
+      <c r="C401" t="s">
+        <v>15</v>
+      </c>
+      <c r="D401">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" t="s">
+        <v>5</v>
+      </c>
+      <c r="B402" t="s">
+        <v>10</v>
+      </c>
+      <c r="D402">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" t="s">
+        <v>5</v>
+      </c>
+      <c r="B403" t="s">
+        <v>10</v>
+      </c>
+      <c r="D403">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" t="s">
+        <v>6</v>
+      </c>
+      <c r="B404" t="s">
+        <v>11</v>
+      </c>
+      <c r="C404" t="s">
+        <v>15</v>
+      </c>
+      <c r="D404">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" t="s">
+        <v>5</v>
+      </c>
+      <c r="B405" t="s">
+        <v>10</v>
+      </c>
+      <c r="D405">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" t="s">
+        <v>5</v>
+      </c>
+      <c r="B406" t="s">
+        <v>10</v>
+      </c>
+      <c r="D406">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" t="s">
+        <v>6</v>
+      </c>
+      <c r="B407" t="s">
+        <v>11</v>
+      </c>
+      <c r="C407" t="s">
+        <v>15</v>
+      </c>
+      <c r="D407">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" t="s">
+        <v>6</v>
+      </c>
+      <c r="B408" t="s">
+        <v>11</v>
+      </c>
+      <c r="C408" t="s">
+        <v>15</v>
+      </c>
+      <c r="D408">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" t="s">
+        <v>6</v>
+      </c>
+      <c r="B409" t="s">
+        <v>11</v>
+      </c>
+      <c r="C409" t="s">
+        <v>15</v>
+      </c>
+      <c r="D409">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" t="s">
+        <v>5</v>
+      </c>
+      <c r="B410" t="s">
+        <v>10</v>
+      </c>
+      <c r="D410">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" t="s">
+        <v>6</v>
+      </c>
+      <c r="B411" t="s">
+        <v>11</v>
+      </c>
+      <c r="C411" t="s">
+        <v>15</v>
+      </c>
+      <c r="D411">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" t="s">
+        <v>5</v>
+      </c>
+      <c r="B412" t="s">
+        <v>10</v>
+      </c>
+      <c r="D412">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" t="s">
+        <v>5</v>
+      </c>
+      <c r="B413" t="s">
+        <v>10</v>
+      </c>
+      <c r="D413">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" t="s">
+        <v>5</v>
+      </c>
+      <c r="B414" t="s">
+        <v>10</v>
+      </c>
+      <c r="D414">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" t="s">
+        <v>5</v>
+      </c>
+      <c r="B415" t="s">
+        <v>10</v>
+      </c>
+      <c r="D415">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" t="s">
+        <v>5</v>
+      </c>
+      <c r="B416" t="s">
+        <v>10</v>
+      </c>
+      <c r="D416">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" t="s">
+        <v>5</v>
+      </c>
+      <c r="B417" t="s">
+        <v>10</v>
+      </c>
+      <c r="D417">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" t="s">
+        <v>5</v>
+      </c>
+      <c r="B418" t="s">
+        <v>10</v>
+      </c>
+      <c r="D418">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" t="s">
+        <v>5</v>
+      </c>
+      <c r="B419" t="s">
+        <v>10</v>
+      </c>
+      <c r="D419">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" t="s">
+        <v>6</v>
+      </c>
+      <c r="B420" t="s">
+        <v>11</v>
+      </c>
+      <c r="C420" t="s">
+        <v>15</v>
+      </c>
+      <c r="D420">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" t="s">
+        <v>6</v>
+      </c>
+      <c r="B421" t="s">
+        <v>11</v>
+      </c>
+      <c r="C421" t="s">
+        <v>15</v>
+      </c>
+      <c r="D421">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" t="s">
+        <v>11</v>
+      </c>
+      <c r="C422" t="s">
+        <v>15</v>
+      </c>
+      <c r="D422">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" t="s">
+        <v>6</v>
+      </c>
+      <c r="B423" t="s">
+        <v>11</v>
+      </c>
+      <c r="C423" t="s">
+        <v>15</v>
+      </c>
+      <c r="D423">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" t="s">
+        <v>6</v>
+      </c>
+      <c r="B424" t="s">
+        <v>11</v>
+      </c>
+      <c r="C424" t="s">
+        <v>15</v>
+      </c>
+      <c r="D424">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" t="s">
+        <v>6</v>
+      </c>
+      <c r="B425" t="s">
+        <v>11</v>
+      </c>
+      <c r="C425" t="s">
+        <v>15</v>
+      </c>
+      <c r="D425">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
+      <c r="A426" t="s">
+        <v>5</v>
+      </c>
+      <c r="B426" t="s">
+        <v>10</v>
+      </c>
+      <c r="D426">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
+      <c r="A427" t="s">
+        <v>5</v>
+      </c>
+      <c r="B427" t="s">
+        <v>10</v>
+      </c>
+      <c r="D427">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4">
+      <c r="A428" t="s">
+        <v>6</v>
+      </c>
+      <c r="B428" t="s">
+        <v>11</v>
+      </c>
+      <c r="C428" t="s">
+        <v>15</v>
+      </c>
+      <c r="D428">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
+      <c r="A429" t="s">
+        <v>5</v>
+      </c>
+      <c r="B429" t="s">
+        <v>10</v>
+      </c>
+      <c r="D429">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" t="s">
+        <v>5</v>
+      </c>
+      <c r="B430" t="s">
+        <v>10</v>
+      </c>
+      <c r="D430">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
+      <c r="A431" t="s">
+        <v>5</v>
+      </c>
+      <c r="B431" t="s">
+        <v>10</v>
+      </c>
+      <c r="D431">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4">
+      <c r="A432" t="s">
+        <v>6</v>
+      </c>
+      <c r="B432" t="s">
+        <v>11</v>
+      </c>
+      <c r="C432" t="s">
+        <v>15</v>
+      </c>
+      <c r="D432">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4">
+      <c r="A433" t="s">
+        <v>5</v>
+      </c>
+      <c r="B433" t="s">
+        <v>10</v>
+      </c>
+      <c r="D433">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
+      <c r="A434" t="s">
+        <v>5</v>
+      </c>
+      <c r="B434" t="s">
+        <v>10</v>
+      </c>
+      <c r="D434">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
+      <c r="A435" t="s">
+        <v>6</v>
+      </c>
+      <c r="B435" t="s">
+        <v>11</v>
+      </c>
+      <c r="C435" t="s">
+        <v>15</v>
+      </c>
+      <c r="D435">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436" t="s">
+        <v>6</v>
+      </c>
+      <c r="B436" t="s">
+        <v>11</v>
+      </c>
+      <c r="C436" t="s">
+        <v>15</v>
+      </c>
+      <c r="D436">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4">
+      <c r="A437" t="s">
+        <v>6</v>
+      </c>
+      <c r="B437" t="s">
+        <v>11</v>
+      </c>
+      <c r="C437" t="s">
+        <v>15</v>
+      </c>
+      <c r="D437">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
+      <c r="A438" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" t="s">
+        <v>11</v>
+      </c>
+      <c r="C438" t="s">
+        <v>15</v>
+      </c>
+      <c r="D438">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
+      <c r="A439" t="s">
+        <v>6</v>
+      </c>
+      <c r="B439" t="s">
+        <v>11</v>
+      </c>
+      <c r="C439" t="s">
+        <v>15</v>
+      </c>
+      <c r="D439">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440" t="s">
+        <v>6</v>
+      </c>
+      <c r="B440" t="s">
+        <v>11</v>
+      </c>
+      <c r="C440" t="s">
+        <v>15</v>
+      </c>
+      <c r="D440">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441" t="s">
+        <v>6</v>
+      </c>
+      <c r="B441" t="s">
+        <v>11</v>
+      </c>
+      <c r="C441" t="s">
+        <v>15</v>
+      </c>
+      <c r="D441">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442" t="s">
+        <v>5</v>
+      </c>
+      <c r="B442" t="s">
+        <v>10</v>
+      </c>
+      <c r="D442">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443" t="s">
+        <v>6</v>
+      </c>
+      <c r="B443" t="s">
+        <v>11</v>
+      </c>
+      <c r="C443" t="s">
+        <v>15</v>
+      </c>
+      <c r="D443">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" t="s">
+        <v>5</v>
+      </c>
+      <c r="B444" t="s">
+        <v>10</v>
+      </c>
+      <c r="D444">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" t="s">
+        <v>5</v>
+      </c>
+      <c r="B445" t="s">
+        <v>10</v>
+      </c>
+      <c r="D445">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" t="s">
+        <v>6</v>
+      </c>
+      <c r="B446" t="s">
+        <v>11</v>
+      </c>
+      <c r="C446" t="s">
+        <v>15</v>
+      </c>
+      <c r="D446">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" t="s">
+        <v>11</v>
+      </c>
+      <c r="C447" t="s">
+        <v>15</v>
+      </c>
+      <c r="D447">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" t="s">
+        <v>5</v>
+      </c>
+      <c r="B448" t="s">
+        <v>10</v>
+      </c>
+      <c r="D448">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" t="s">
+        <v>5</v>
+      </c>
+      <c r="B449" t="s">
+        <v>10</v>
+      </c>
+      <c r="D449">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" t="s">
+        <v>5</v>
+      </c>
+      <c r="B450" t="s">
+        <v>10</v>
+      </c>
+      <c r="D450">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" t="s">
+        <v>5</v>
+      </c>
+      <c r="B451" t="s">
+        <v>10</v>
+      </c>
+      <c r="D451">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" t="s">
+        <v>6</v>
+      </c>
+      <c r="B452" t="s">
+        <v>11</v>
+      </c>
+      <c r="C452" t="s">
+        <v>15</v>
+      </c>
+      <c r="D452">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" t="s">
+        <v>5</v>
+      </c>
+      <c r="B453" t="s">
+        <v>10</v>
+      </c>
+      <c r="D453">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" t="s">
+        <v>6</v>
+      </c>
+      <c r="B454" t="s">
+        <v>11</v>
+      </c>
+      <c r="C454" t="s">
+        <v>15</v>
+      </c>
+      <c r="D454">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" t="s">
+        <v>11</v>
+      </c>
+      <c r="C455" t="s">
+        <v>15</v>
+      </c>
+      <c r="D455">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" t="s">
+        <v>6</v>
+      </c>
+      <c r="B456" t="s">
+        <v>11</v>
+      </c>
+      <c r="C456" t="s">
+        <v>15</v>
+      </c>
+      <c r="D456">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" t="s">
+        <v>6</v>
+      </c>
+      <c r="B457" t="s">
+        <v>11</v>
+      </c>
+      <c r="C457" t="s">
+        <v>15</v>
+      </c>
+      <c r="D457">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" t="s">
+        <v>6</v>
+      </c>
+      <c r="B458" t="s">
+        <v>11</v>
+      </c>
+      <c r="C458" t="s">
+        <v>15</v>
+      </c>
+      <c r="D458">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" t="s">
+        <v>6</v>
+      </c>
+      <c r="B459" t="s">
+        <v>11</v>
+      </c>
+      <c r="C459" t="s">
+        <v>15</v>
+      </c>
+      <c r="D459">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" t="s">
+        <v>6</v>
+      </c>
+      <c r="B460" t="s">
+        <v>11</v>
+      </c>
+      <c r="C460" t="s">
+        <v>15</v>
+      </c>
+      <c r="D460">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" t="s">
+        <v>6</v>
+      </c>
+      <c r="B461" t="s">
+        <v>11</v>
+      </c>
+      <c r="C461" t="s">
+        <v>15</v>
+      </c>
+      <c r="D461">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" t="s">
+        <v>6</v>
+      </c>
+      <c r="B462" t="s">
+        <v>11</v>
+      </c>
+      <c r="C462" t="s">
+        <v>15</v>
+      </c>
+      <c r="D462">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" t="s">
+        <v>5</v>
+      </c>
+      <c r="B463" t="s">
+        <v>10</v>
+      </c>
+      <c r="D463">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" t="s">
+        <v>5</v>
+      </c>
+      <c r="B464" t="s">
+        <v>10</v>
+      </c>
+      <c r="D464">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" t="s">
+        <v>5</v>
+      </c>
+      <c r="B465" t="s">
+        <v>10</v>
+      </c>
+      <c r="D465">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" t="s">
+        <v>5</v>
+      </c>
+      <c r="B466" t="s">
+        <v>10</v>
+      </c>
+      <c r="D466">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" t="s">
+        <v>5</v>
+      </c>
+      <c r="B467" t="s">
+        <v>10</v>
+      </c>
+      <c r="D467">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" t="s">
+        <v>5</v>
+      </c>
+      <c r="B468" t="s">
+        <v>10</v>
+      </c>
+      <c r="D468">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" t="s">
+        <v>5</v>
+      </c>
+      <c r="B469" t="s">
+        <v>10</v>
+      </c>
+      <c r="D469">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" t="s">
+        <v>6</v>
+      </c>
+      <c r="B470" t="s">
+        <v>11</v>
+      </c>
+      <c r="C470" t="s">
+        <v>15</v>
+      </c>
+      <c r="D470">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" t="s">
+        <v>5</v>
+      </c>
+      <c r="B471" t="s">
+        <v>10</v>
+      </c>
+      <c r="D471">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" t="s">
+        <v>6</v>
+      </c>
+      <c r="B472" t="s">
+        <v>11</v>
+      </c>
+      <c r="C472" t="s">
+        <v>15</v>
+      </c>
+      <c r="D472">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" t="s">
+        <v>5</v>
+      </c>
+      <c r="B473" t="s">
+        <v>10</v>
+      </c>
+      <c r="D473">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474" t="s">
+        <v>6</v>
+      </c>
+      <c r="B474" t="s">
+        <v>11</v>
+      </c>
+      <c r="C474" t="s">
+        <v>15</v>
+      </c>
+      <c r="D474">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475" t="s">
+        <v>6</v>
+      </c>
+      <c r="B475" t="s">
+        <v>11</v>
+      </c>
+      <c r="C475" t="s">
+        <v>15</v>
+      </c>
+      <c r="D475">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
+      <c r="A476" t="s">
+        <v>6</v>
+      </c>
+      <c r="B476" t="s">
+        <v>11</v>
+      </c>
+      <c r="C476" t="s">
+        <v>15</v>
+      </c>
+      <c r="D476">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
+      <c r="A477" t="s">
+        <v>5</v>
+      </c>
+      <c r="B477" t="s">
+        <v>10</v>
+      </c>
+      <c r="D477">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
+      <c r="A478" t="s">
+        <v>5</v>
+      </c>
+      <c r="B478" t="s">
+        <v>10</v>
+      </c>
+      <c r="D478">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
+      <c r="A479" t="s">
+        <v>5</v>
+      </c>
+      <c r="B479" t="s">
+        <v>10</v>
+      </c>
+      <c r="D479">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480" t="s">
+        <v>6</v>
+      </c>
+      <c r="B480" t="s">
+        <v>11</v>
+      </c>
+      <c r="C480" t="s">
+        <v>15</v>
+      </c>
+      <c r="D480">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4">
+      <c r="A481" t="s">
+        <v>6</v>
+      </c>
+      <c r="B481" t="s">
+        <v>11</v>
+      </c>
+      <c r="C481" t="s">
+        <v>15</v>
+      </c>
+      <c r="D481">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4">
+      <c r="A482" t="s">
+        <v>6</v>
+      </c>
+      <c r="B482" t="s">
+        <v>11</v>
+      </c>
+      <c r="C482" t="s">
+        <v>15</v>
+      </c>
+      <c r="D482">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4">
+      <c r="A483" t="s">
+        <v>5</v>
+      </c>
+      <c r="B483" t="s">
+        <v>10</v>
+      </c>
+      <c r="D483">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4">
+      <c r="A484" t="s">
+        <v>5</v>
+      </c>
+      <c r="B484" t="s">
+        <v>10</v>
+      </c>
+      <c r="D484">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4">
+      <c r="A485" t="s">
+        <v>5</v>
+      </c>
+      <c r="B485" t="s">
+        <v>10</v>
+      </c>
+      <c r="D485">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4">
+      <c r="A486" t="s">
+        <v>5</v>
+      </c>
+      <c r="B486" t="s">
+        <v>10</v>
+      </c>
+      <c r="D486">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4">
+      <c r="A487" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" t="s">
+        <v>11</v>
+      </c>
+      <c r="C487" t="s">
+        <v>15</v>
+      </c>
+      <c r="D487">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4">
+      <c r="A488" t="s">
+        <v>5</v>
+      </c>
+      <c r="B488" t="s">
+        <v>10</v>
+      </c>
+      <c r="D488">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4">
+      <c r="A489" t="s">
+        <v>5</v>
+      </c>
+      <c r="B489" t="s">
+        <v>10</v>
+      </c>
+      <c r="D489">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4">
+      <c r="A490" t="s">
+        <v>5</v>
+      </c>
+      <c r="B490" t="s">
+        <v>10</v>
+      </c>
+      <c r="D490">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4">
+      <c r="A491" t="s">
+        <v>6</v>
+      </c>
+      <c r="B491" t="s">
+        <v>11</v>
+      </c>
+      <c r="C491" t="s">
+        <v>15</v>
+      </c>
+      <c r="D491">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4">
+      <c r="A492" t="s">
+        <v>6</v>
+      </c>
+      <c r="B492" t="s">
+        <v>11</v>
+      </c>
+      <c r="C492" t="s">
+        <v>15</v>
+      </c>
+      <c r="D492">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4">
+      <c r="A493" t="s">
+        <v>5</v>
+      </c>
+      <c r="B493" t="s">
+        <v>10</v>
+      </c>
+      <c r="D493">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4">
+      <c r="A494" t="s">
+        <v>5</v>
+      </c>
+      <c r="B494" t="s">
+        <v>10</v>
+      </c>
+      <c r="D494">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4">
+      <c r="A495" t="s">
+        <v>5</v>
+      </c>
+      <c r="B495" t="s">
+        <v>10</v>
+      </c>
+      <c r="D495">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4">
+      <c r="A496" t="s">
+        <v>5</v>
+      </c>
+      <c r="B496" t="s">
+        <v>10</v>
+      </c>
+      <c r="D496">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4">
+      <c r="A497" t="s">
+        <v>5</v>
+      </c>
+      <c r="B497" t="s">
+        <v>10</v>
+      </c>
+      <c r="D497">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4">
+      <c r="A498" t="s">
+        <v>5</v>
+      </c>
+      <c r="B498" t="s">
+        <v>10</v>
+      </c>
+      <c r="D498">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4">
+      <c r="A499" t="s">
+        <v>6</v>
+      </c>
+      <c r="B499" t="s">
+        <v>11</v>
+      </c>
+      <c r="C499" t="s">
+        <v>15</v>
+      </c>
+      <c r="D499">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4">
+      <c r="A500" t="s">
+        <v>5</v>
+      </c>
+      <c r="B500" t="s">
+        <v>10</v>
+      </c>
+      <c r="D500">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4">
+      <c r="A501" t="s">
+        <v>5</v>
+      </c>
+      <c r="B501" t="s">
+        <v>10</v>
+      </c>
+      <c r="D501">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4">
+      <c r="A502" t="s">
+        <v>5</v>
+      </c>
+      <c r="B502" t="s">
+        <v>10</v>
+      </c>
+      <c r="D502">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4">
+      <c r="A503" t="s">
+        <v>6</v>
+      </c>
+      <c r="B503" t="s">
+        <v>11</v>
+      </c>
+      <c r="C503" t="s">
+        <v>15</v>
+      </c>
+      <c r="D503">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" t="s">
+        <v>11</v>
+      </c>
+      <c r="C504" t="s">
+        <v>15</v>
+      </c>
+      <c r="D504">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505" t="s">
+        <v>6</v>
+      </c>
+      <c r="B505" t="s">
+        <v>11</v>
+      </c>
+      <c r="C505" t="s">
+        <v>15</v>
+      </c>
+      <c r="D505">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506" t="s">
+        <v>5</v>
+      </c>
+      <c r="B506" t="s">
+        <v>10</v>
+      </c>
+      <c r="D506">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4">
+      <c r="A507" t="s">
+        <v>5</v>
+      </c>
+      <c r="B507" t="s">
+        <v>10</v>
+      </c>
+      <c r="D507">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
+      <c r="A508" t="s">
+        <v>5</v>
+      </c>
+      <c r="B508" t="s">
+        <v>10</v>
+      </c>
+      <c r="D508">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
+      <c r="A509" t="s">
+        <v>5</v>
+      </c>
+      <c r="B509" t="s">
+        <v>10</v>
+      </c>
+      <c r="D509">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510" t="s">
+        <v>5</v>
+      </c>
+      <c r="B510" t="s">
+        <v>10</v>
+      </c>
+      <c r="D510">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
+      <c r="A511" t="s">
+        <v>5</v>
+      </c>
+      <c r="B511" t="s">
+        <v>10</v>
+      </c>
+      <c r="D511">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
+      <c r="A512" t="s">
+        <v>5</v>
+      </c>
+      <c r="B512" t="s">
+        <v>10</v>
+      </c>
+      <c r="D512">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
+      <c r="A513" t="s">
+        <v>5</v>
+      </c>
+      <c r="B513" t="s">
+        <v>10</v>
+      </c>
+      <c r="D513">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4">
+      <c r="A514" t="s">
         <v>7</v>
       </c>
-      <c r="C67" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67">
-        <v>197</v>
+      <c r="B514" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4">
+      <c r="A515" t="s">
+        <v>7</v>
+      </c>
+      <c r="B515" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/out/thesis/tables/warnings.xlsx
+++ b/out/thesis/tables/warnings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="16">
   <si>
     <t>category</t>
   </si>
@@ -393,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D515"/>
+  <dimension ref="A1:D470"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -440,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>28</v>
@@ -451,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -462,10 +462,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -476,7 +476,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -484,10 +484,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -495,10 +495,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -506,10 +506,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -517,10 +517,10 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -531,7 +531,7 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -539,10 +539,10 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -550,10 +550,10 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -564,7 +564,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -572,10 +572,10 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -583,10 +583,10 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -597,7 +597,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -608,7 +608,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -619,7 +619,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -630,7 +630,7 @@
         <v>10</v>
       </c>
       <c r="D21">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -641,7 +641,7 @@
         <v>10</v>
       </c>
       <c r="D22">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -652,7 +652,7 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -663,7 +663,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -674,7 +674,7 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -685,7 +685,7 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -696,7 +696,7 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -718,7 +718,7 @@
         <v>10</v>
       </c>
       <c r="D29">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -729,7 +729,7 @@
         <v>10</v>
       </c>
       <c r="D30">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -740,7 +740,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -751,7 +751,7 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -762,7 +762,7 @@
         <v>10</v>
       </c>
       <c r="D33">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -773,7 +773,7 @@
         <v>10</v>
       </c>
       <c r="D34">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -784,7 +784,7 @@
         <v>10</v>
       </c>
       <c r="D35">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -795,7 +795,7 @@
         <v>10</v>
       </c>
       <c r="D36">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -806,7 +806,7 @@
         <v>10</v>
       </c>
       <c r="D37">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -817,7 +817,7 @@
         <v>10</v>
       </c>
       <c r="D38">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -828,7 +828,7 @@
         <v>10</v>
       </c>
       <c r="D39">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -850,7 +850,7 @@
         <v>10</v>
       </c>
       <c r="D41">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -861,7 +861,7 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
       <c r="D43">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -883,7 +883,7 @@
         <v>10</v>
       </c>
       <c r="D44">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -894,7 +894,7 @@
         <v>10</v>
       </c>
       <c r="D45">
-        <v>83</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -905,7 +905,7 @@
         <v>10</v>
       </c>
       <c r="D46">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -916,7 +916,7 @@
         <v>10</v>
       </c>
       <c r="D47">
-        <v>90</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -927,7 +927,7 @@
         <v>10</v>
       </c>
       <c r="D48">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="D49">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -949,7 +949,7 @@
         <v>10</v>
       </c>
       <c r="D50">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -960,7 +960,7 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>94</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -971,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="D52">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -982,7 +982,7 @@
         <v>10</v>
       </c>
       <c r="D53">
-        <v>96</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -993,7 +993,7 @@
         <v>10</v>
       </c>
       <c r="D54">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="D55">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1015,7 +1015,7 @@
         <v>10</v>
       </c>
       <c r="D56">
-        <v>100</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1026,7 +1026,7 @@
         <v>10</v>
       </c>
       <c r="D57">
-        <v>104</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1037,7 +1037,7 @@
         <v>10</v>
       </c>
       <c r="D58">
-        <v>109</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1048,7 +1048,7 @@
         <v>10</v>
       </c>
       <c r="D59">
-        <v>111</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1059,7 +1059,7 @@
         <v>10</v>
       </c>
       <c r="D60">
-        <v>112</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1070,7 +1070,7 @@
         <v>10</v>
       </c>
       <c r="D61">
-        <v>114</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1081,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="D62">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1092,7 +1092,7 @@
         <v>10</v>
       </c>
       <c r="D63">
-        <v>116</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1103,7 +1103,7 @@
         <v>10</v>
       </c>
       <c r="D64">
-        <v>117</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1114,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="D65">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
       <c r="D66">
-        <v>119</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1136,7 +1136,7 @@
         <v>10</v>
       </c>
       <c r="D67">
-        <v>120</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1147,7 +1147,7 @@
         <v>10</v>
       </c>
       <c r="D68">
-        <v>121</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1158,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="D69">
-        <v>123</v>
+        <v>154</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1169,7 +1169,7 @@
         <v>10</v>
       </c>
       <c r="D70">
-        <v>130</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1180,7 +1180,7 @@
         <v>10</v>
       </c>
       <c r="D71">
-        <v>138</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1191,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="D72">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1202,7 +1202,7 @@
         <v>10</v>
       </c>
       <c r="D73">
-        <v>143</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1213,7 +1213,7 @@
         <v>10</v>
       </c>
       <c r="D74">
-        <v>145</v>
+        <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1224,7 +1224,7 @@
         <v>10</v>
       </c>
       <c r="D75">
-        <v>146</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="D76">
-        <v>147</v>
+        <v>162</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1246,7 +1246,7 @@
         <v>10</v>
       </c>
       <c r="D77">
-        <v>149</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1257,7 +1257,7 @@
         <v>10</v>
       </c>
       <c r="D78">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1268,7 +1268,7 @@
         <v>10</v>
       </c>
       <c r="D79">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1279,7 +1279,7 @@
         <v>10</v>
       </c>
       <c r="D80">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1290,7 +1290,7 @@
         <v>10</v>
       </c>
       <c r="D81">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1301,7 +1301,7 @@
         <v>10</v>
       </c>
       <c r="D82">
-        <v>155</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1312,7 +1312,7 @@
         <v>10</v>
       </c>
       <c r="D83">
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1323,7 +1323,7 @@
         <v>10</v>
       </c>
       <c r="D84">
-        <v>157</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1334,7 +1334,7 @@
         <v>10</v>
       </c>
       <c r="D85">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1345,7 +1345,7 @@
         <v>10</v>
       </c>
       <c r="D86">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1356,7 +1356,7 @@
         <v>10</v>
       </c>
       <c r="D87">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1367,7 +1367,7 @@
         <v>10</v>
       </c>
       <c r="D88">
-        <v>162</v>
+        <v>181</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1378,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="D89">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1389,7 +1389,7 @@
         <v>10</v>
       </c>
       <c r="D90">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1400,7 +1400,7 @@
         <v>10</v>
       </c>
       <c r="D91">
-        <v>169</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1411,7 +1411,7 @@
         <v>10</v>
       </c>
       <c r="D92">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1422,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="D93">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1433,7 +1433,7 @@
         <v>10</v>
       </c>
       <c r="D94">
-        <v>172</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1444,7 +1444,7 @@
         <v>10</v>
       </c>
       <c r="D95">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1455,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="D96">
-        <v>174</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1466,7 +1466,7 @@
         <v>10</v>
       </c>
       <c r="D97">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1477,7 +1477,7 @@
         <v>10</v>
       </c>
       <c r="D98">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
       <c r="D99">
-        <v>177</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1499,7 +1499,7 @@
         <v>10</v>
       </c>
       <c r="D100">
-        <v>178</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1510,7 +1510,7 @@
         <v>10</v>
       </c>
       <c r="D101">
-        <v>181</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1521,7 +1521,7 @@
         <v>10</v>
       </c>
       <c r="D102">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1532,7 +1532,7 @@
         <v>10</v>
       </c>
       <c r="D103">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1543,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="D104">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1554,7 +1554,7 @@
         <v>10</v>
       </c>
       <c r="D105">
-        <v>185</v>
+        <v>202</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1565,7 +1565,7 @@
         <v>10</v>
       </c>
       <c r="D106">
-        <v>186</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1576,7 +1576,7 @@
         <v>10</v>
       </c>
       <c r="D107">
-        <v>187</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1587,7 +1587,7 @@
         <v>10</v>
       </c>
       <c r="D108">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1598,7 +1598,7 @@
         <v>10</v>
       </c>
       <c r="D109">
-        <v>189</v>
+        <v>206</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1609,7 +1609,7 @@
         <v>10</v>
       </c>
       <c r="D110">
-        <v>191</v>
+        <v>207</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1617,10 +1617,10 @@
         <v>5</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D111">
-        <v>192</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1628,10 +1628,10 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D112">
-        <v>193</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1639,10 +1639,10 @@
         <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D113">
-        <v>194</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1653,7 +1653,7 @@
         <v>10</v>
       </c>
       <c r="D114">
-        <v>198</v>
+        <v>42</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -1664,7 +1664,7 @@
         <v>10</v>
       </c>
       <c r="D115">
-        <v>199</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -1675,7 +1675,7 @@
         <v>10</v>
       </c>
       <c r="D116">
-        <v>200</v>
+        <v>45</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -1686,7 +1686,7 @@
         <v>10</v>
       </c>
       <c r="D117">
-        <v>201</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -1697,7 +1697,7 @@
         <v>10</v>
       </c>
       <c r="D118">
-        <v>202</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>10</v>
       </c>
       <c r="D119">
-        <v>203</v>
+        <v>50</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -1719,7 +1719,7 @@
         <v>10</v>
       </c>
       <c r="D120">
-        <v>204</v>
+        <v>51</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -1730,7 +1730,7 @@
         <v>10</v>
       </c>
       <c r="D121">
-        <v>205</v>
+        <v>53</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -1741,7 +1741,7 @@
         <v>10</v>
       </c>
       <c r="D122">
-        <v>206</v>
+        <v>54</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -1752,7 +1752,7 @@
         <v>10</v>
       </c>
       <c r="D123">
-        <v>207</v>
+        <v>57</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -1760,10 +1760,10 @@
         <v>5</v>
       </c>
       <c r="B124" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D124">
-        <v>28</v>
+        <v>58</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -1771,10 +1771,10 @@
         <v>5</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D125">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -1782,10 +1782,10 @@
         <v>5</v>
       </c>
       <c r="B126" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D126">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -1793,10 +1793,10 @@
         <v>5</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D127">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -1804,10 +1804,10 @@
         <v>5</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D128">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -1815,10 +1815,10 @@
         <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D129">
-        <v>37</v>
+        <v>65</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -1826,10 +1826,10 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D130">
-        <v>39</v>
+        <v>67</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -1837,10 +1837,10 @@
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D131">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -1851,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="D132">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>10</v>
       </c>
       <c r="D133">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D134">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -1884,7 +1884,7 @@
         <v>10</v>
       </c>
       <c r="D135">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -1892,10 +1892,10 @@
         <v>5</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D136">
-        <v>46</v>
+        <v>77</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -1903,10 +1903,10 @@
         <v>5</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D137">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="D138">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -1928,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="D139">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -1939,7 +1939,7 @@
         <v>10</v>
       </c>
       <c r="D140">
-        <v>50</v>
+        <v>81</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -1950,7 +1950,7 @@
         <v>10</v>
       </c>
       <c r="D141">
-        <v>51</v>
+        <v>82</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -1961,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="D142">
-        <v>52</v>
+        <v>83</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -1972,7 +1972,7 @@
         <v>10</v>
       </c>
       <c r="D143">
-        <v>53</v>
+        <v>84</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -1983,7 +1983,7 @@
         <v>10</v>
       </c>
       <c r="D144">
-        <v>54</v>
+        <v>91</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -1994,7 +1994,7 @@
         <v>10</v>
       </c>
       <c r="D145">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2005,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="D146">
-        <v>58</v>
+        <v>93</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>10</v>
       </c>
       <c r="D147">
-        <v>59</v>
+        <v>95</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2027,7 +2027,7 @@
         <v>10</v>
       </c>
       <c r="D148">
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2038,7 +2038,7 @@
         <v>10</v>
       </c>
       <c r="D149">
-        <v>61</v>
+        <v>97</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2049,7 +2049,7 @@
         <v>10</v>
       </c>
       <c r="D150">
-        <v>64</v>
+        <v>99</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2060,7 +2060,7 @@
         <v>10</v>
       </c>
       <c r="D151">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2071,7 +2071,7 @@
         <v>10</v>
       </c>
       <c r="D152">
-        <v>67</v>
+        <v>109</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2082,7 +2082,7 @@
         <v>10</v>
       </c>
       <c r="D153">
-        <v>68</v>
+        <v>111</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2093,7 +2093,7 @@
         <v>10</v>
       </c>
       <c r="D154">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2104,7 +2104,7 @@
         <v>10</v>
       </c>
       <c r="D155">
-        <v>72</v>
+        <v>115</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2115,7 +2115,7 @@
         <v>10</v>
       </c>
       <c r="D156">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2126,7 +2126,7 @@
         <v>10</v>
       </c>
       <c r="D157">
-        <v>75</v>
+        <v>117</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2137,7 +2137,7 @@
         <v>10</v>
       </c>
       <c r="D158">
-        <v>77</v>
+        <v>118</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2148,7 +2148,7 @@
         <v>10</v>
       </c>
       <c r="D159">
-        <v>78</v>
+        <v>119</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2159,7 +2159,7 @@
         <v>10</v>
       </c>
       <c r="D160">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>10</v>
       </c>
       <c r="D161">
-        <v>80</v>
+        <v>121</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2181,7 +2181,7 @@
         <v>10</v>
       </c>
       <c r="D162">
-        <v>81</v>
+        <v>123</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2192,7 +2192,7 @@
         <v>10</v>
       </c>
       <c r="D163">
-        <v>82</v>
+        <v>130</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2203,7 +2203,7 @@
         <v>10</v>
       </c>
       <c r="D164">
-        <v>83</v>
+        <v>138</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2214,7 +2214,7 @@
         <v>10</v>
       </c>
       <c r="D165">
-        <v>84</v>
+        <v>142</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2225,7 +2225,7 @@
         <v>10</v>
       </c>
       <c r="D166">
-        <v>90</v>
+        <v>143</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2236,7 +2236,7 @@
         <v>10</v>
       </c>
       <c r="D167">
-        <v>91</v>
+        <v>145</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2247,7 +2247,7 @@
         <v>10</v>
       </c>
       <c r="D168">
-        <v>92</v>
+        <v>146</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2258,7 +2258,7 @@
         <v>10</v>
       </c>
       <c r="D169">
-        <v>93</v>
+        <v>147</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2269,7 +2269,7 @@
         <v>10</v>
       </c>
       <c r="D170">
-        <v>94</v>
+        <v>149</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2280,7 +2280,7 @@
         <v>10</v>
       </c>
       <c r="D171">
-        <v>95</v>
+        <v>150</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2291,7 +2291,7 @@
         <v>10</v>
       </c>
       <c r="D172">
-        <v>96</v>
+        <v>151</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2302,7 +2302,7 @@
         <v>10</v>
       </c>
       <c r="D173">
-        <v>97</v>
+        <v>153</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2313,7 +2313,7 @@
         <v>10</v>
       </c>
       <c r="D174">
-        <v>99</v>
+        <v>154</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>10</v>
       </c>
       <c r="D175">
-        <v>100</v>
+        <v>155</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2335,7 +2335,7 @@
         <v>10</v>
       </c>
       <c r="D176">
-        <v>104</v>
+        <v>156</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2346,7 +2346,7 @@
         <v>10</v>
       </c>
       <c r="D177">
-        <v>109</v>
+        <v>157</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2357,7 +2357,7 @@
         <v>10</v>
       </c>
       <c r="D178">
-        <v>111</v>
+        <v>158</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2368,7 +2368,7 @@
         <v>10</v>
       </c>
       <c r="D179">
-        <v>112</v>
+        <v>161</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2379,7 +2379,7 @@
         <v>10</v>
       </c>
       <c r="D180">
-        <v>114</v>
+        <v>162</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2390,7 +2390,7 @@
         <v>10</v>
       </c>
       <c r="D181">
-        <v>115</v>
+        <v>163</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2401,7 +2401,7 @@
         <v>10</v>
       </c>
       <c r="D182">
-        <v>116</v>
+        <v>167</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2412,7 +2412,7 @@
         <v>10</v>
       </c>
       <c r="D183">
-        <v>117</v>
+        <v>169</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2423,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="D184">
-        <v>118</v>
+        <v>170</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2434,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="D185">
-        <v>119</v>
+        <v>171</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -2445,7 +2445,7 @@
         <v>10</v>
       </c>
       <c r="D186">
-        <v>120</v>
+        <v>172</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -2456,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="D187">
-        <v>121</v>
+        <v>174</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -2467,7 +2467,7 @@
         <v>10</v>
       </c>
       <c r="D188">
-        <v>123</v>
+        <v>175</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>10</v>
       </c>
       <c r="D189">
-        <v>130</v>
+        <v>176</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -2489,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="D190">
-        <v>138</v>
+        <v>177</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -2500,7 +2500,7 @@
         <v>10</v>
       </c>
       <c r="D191">
-        <v>142</v>
+        <v>178</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -2511,7 +2511,7 @@
         <v>10</v>
       </c>
       <c r="D192">
-        <v>143</v>
+        <v>181</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -2522,7 +2522,7 @@
         <v>10</v>
       </c>
       <c r="D193">
-        <v>145</v>
+        <v>182</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -2533,7 +2533,7 @@
         <v>10</v>
       </c>
       <c r="D194">
-        <v>146</v>
+        <v>183</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -2544,7 +2544,7 @@
         <v>10</v>
       </c>
       <c r="D195">
-        <v>147</v>
+        <v>184</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -2555,7 +2555,7 @@
         <v>10</v>
       </c>
       <c r="D196">
-        <v>149</v>
+        <v>185</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -2566,7 +2566,7 @@
         <v>10</v>
       </c>
       <c r="D197">
-        <v>150</v>
+        <v>186</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -2577,7 +2577,7 @@
         <v>10</v>
       </c>
       <c r="D198">
-        <v>151</v>
+        <v>187</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -2588,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="D199">
-        <v>153</v>
+        <v>188</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -2599,7 +2599,7 @@
         <v>10</v>
       </c>
       <c r="D200">
-        <v>154</v>
+        <v>189</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -2610,7 +2610,7 @@
         <v>10</v>
       </c>
       <c r="D201">
-        <v>155</v>
+        <v>191</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -2621,7 +2621,7 @@
         <v>10</v>
       </c>
       <c r="D202">
-        <v>156</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>10</v>
       </c>
       <c r="D203">
-        <v>157</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -2643,7 +2643,7 @@
         <v>10</v>
       </c>
       <c r="D204">
-        <v>158</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -2654,7 +2654,7 @@
         <v>10</v>
       </c>
       <c r="D205">
-        <v>160</v>
+        <v>198</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -2665,7 +2665,7 @@
         <v>10</v>
       </c>
       <c r="D206">
-        <v>161</v>
+        <v>199</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -2676,7 +2676,7 @@
         <v>10</v>
       </c>
       <c r="D207">
-        <v>162</v>
+        <v>200</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -2687,7 +2687,7 @@
         <v>10</v>
       </c>
       <c r="D208">
-        <v>163</v>
+        <v>201</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -2698,7 +2698,7 @@
         <v>10</v>
       </c>
       <c r="D209">
-        <v>167</v>
+        <v>202</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -2709,7 +2709,7 @@
         <v>10</v>
       </c>
       <c r="D210">
-        <v>169</v>
+        <v>203</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -2720,7 +2720,7 @@
         <v>10</v>
       </c>
       <c r="D211">
-        <v>170</v>
+        <v>204</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -2731,7 +2731,7 @@
         <v>10</v>
       </c>
       <c r="D212">
-        <v>171</v>
+        <v>205</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -2742,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="D213">
-        <v>172</v>
+        <v>206</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -2753,7 +2753,7 @@
         <v>10</v>
       </c>
       <c r="D214">
-        <v>173</v>
+        <v>207</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -2761,10 +2761,10 @@
         <v>5</v>
       </c>
       <c r="B215" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D215">
-        <v>174</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -2775,7 +2775,7 @@
         <v>10</v>
       </c>
       <c r="D216">
-        <v>175</v>
+        <v>25</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -2783,10 +2783,10 @@
         <v>5</v>
       </c>
       <c r="B217" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D217">
-        <v>176</v>
+        <v>34</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -2794,10 +2794,10 @@
         <v>5</v>
       </c>
       <c r="B218" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D218">
-        <v>177</v>
+        <v>35</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -2808,7 +2808,7 @@
         <v>10</v>
       </c>
       <c r="D219">
-        <v>178</v>
+        <v>39</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -2819,7 +2819,7 @@
         <v>10</v>
       </c>
       <c r="D220">
-        <v>181</v>
+        <v>42</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -2830,7 +2830,7 @@
         <v>10</v>
       </c>
       <c r="D221">
-        <v>182</v>
+        <v>43</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -2841,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="D222">
-        <v>183</v>
+        <v>45</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -2852,7 +2852,7 @@
         <v>10</v>
       </c>
       <c r="D223">
-        <v>184</v>
+        <v>48</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -2863,7 +2863,7 @@
         <v>10</v>
       </c>
       <c r="D224">
-        <v>185</v>
+        <v>49</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -2874,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="D225">
-        <v>186</v>
+        <v>50</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -2885,7 +2885,7 @@
         <v>10</v>
       </c>
       <c r="D226">
-        <v>187</v>
+        <v>51</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -2896,7 +2896,7 @@
         <v>10</v>
       </c>
       <c r="D227">
-        <v>188</v>
+        <v>53</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -2907,7 +2907,7 @@
         <v>10</v>
       </c>
       <c r="D228">
-        <v>189</v>
+        <v>54</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -2918,7 +2918,7 @@
         <v>10</v>
       </c>
       <c r="D229">
-        <v>191</v>
+        <v>57</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -2929,7 +2929,7 @@
         <v>10</v>
       </c>
       <c r="D230">
-        <v>192</v>
+        <v>58</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -2940,7 +2940,7 @@
         <v>10</v>
       </c>
       <c r="D231">
-        <v>193</v>
+        <v>59</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -2951,7 +2951,7 @@
         <v>10</v>
       </c>
       <c r="D232">
-        <v>194</v>
+        <v>60</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>10</v>
       </c>
       <c r="D233">
-        <v>198</v>
+        <v>61</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -2973,7 +2973,7 @@
         <v>10</v>
       </c>
       <c r="D234">
-        <v>199</v>
+        <v>64</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -2984,7 +2984,7 @@
         <v>10</v>
       </c>
       <c r="D235">
-        <v>200</v>
+        <v>65</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -2995,7 +2995,7 @@
         <v>10</v>
       </c>
       <c r="D236">
-        <v>201</v>
+        <v>67</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3006,7 +3006,7 @@
         <v>10</v>
       </c>
       <c r="D237">
-        <v>202</v>
+        <v>68</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="D238">
-        <v>203</v>
+        <v>71</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3028,7 +3028,7 @@
         <v>10</v>
       </c>
       <c r="D239">
-        <v>204</v>
+        <v>72</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3039,7 +3039,7 @@
         <v>10</v>
       </c>
       <c r="D240">
-        <v>205</v>
+        <v>74</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3050,7 +3050,7 @@
         <v>10</v>
       </c>
       <c r="D241">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3061,7 +3061,7 @@
         <v>10</v>
       </c>
       <c r="D242">
-        <v>207</v>
+        <v>77</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3069,10 +3069,10 @@
         <v>5</v>
       </c>
       <c r="B243" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D243">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3083,7 +3083,7 @@
         <v>10</v>
       </c>
       <c r="D244">
-        <v>25</v>
+        <v>79</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3091,10 +3091,10 @@
         <v>5</v>
       </c>
       <c r="B245" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D245">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3105,7 +3105,7 @@
         <v>10</v>
       </c>
       <c r="D246">
-        <v>31</v>
+        <v>81</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3113,10 +3113,10 @@
         <v>5</v>
       </c>
       <c r="B247" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D247">
-        <v>34</v>
+        <v>82</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3124,10 +3124,10 @@
         <v>5</v>
       </c>
       <c r="B248" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D248">
-        <v>35</v>
+        <v>83</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3135,10 +3135,10 @@
         <v>5</v>
       </c>
       <c r="B249" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D249">
-        <v>36</v>
+        <v>84</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3146,10 +3146,10 @@
         <v>5</v>
       </c>
       <c r="B250" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D250">
-        <v>37</v>
+        <v>91</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3157,10 +3157,10 @@
         <v>5</v>
       </c>
       <c r="B251" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D251">
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3168,10 +3168,10 @@
         <v>5</v>
       </c>
       <c r="B252" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D252">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3182,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="D253">
-        <v>42</v>
+        <v>95</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3190,10 +3190,10 @@
         <v>5</v>
       </c>
       <c r="B254" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D254">
-        <v>43</v>
+        <v>96</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3201,10 +3201,10 @@
         <v>5</v>
       </c>
       <c r="B255" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D255">
-        <v>44</v>
+        <v>97</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3215,7 +3215,7 @@
         <v>10</v>
       </c>
       <c r="D256">
-        <v>45</v>
+        <v>99</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -3223,10 +3223,10 @@
         <v>5</v>
       </c>
       <c r="B257" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D257">
-        <v>46</v>
+        <v>100</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -3234,10 +3234,10 @@
         <v>5</v>
       </c>
       <c r="B258" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D258">
-        <v>47</v>
+        <v>109</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -3248,7 +3248,7 @@
         <v>10</v>
       </c>
       <c r="D259">
-        <v>48</v>
+        <v>111</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -3259,7 +3259,7 @@
         <v>10</v>
       </c>
       <c r="D260">
-        <v>49</v>
+        <v>112</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -3270,7 +3270,7 @@
         <v>10</v>
       </c>
       <c r="D261">
-        <v>50</v>
+        <v>115</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -3281,7 +3281,7 @@
         <v>10</v>
       </c>
       <c r="D262">
-        <v>51</v>
+        <v>116</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -3292,7 +3292,7 @@
         <v>10</v>
       </c>
       <c r="D263">
-        <v>53</v>
+        <v>117</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -3303,7 +3303,7 @@
         <v>10</v>
       </c>
       <c r="D264">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -3314,7 +3314,7 @@
         <v>10</v>
       </c>
       <c r="D265">
-        <v>55</v>
+        <v>119</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -3325,7 +3325,7 @@
         <v>10</v>
       </c>
       <c r="D266">
-        <v>56</v>
+        <v>120</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -3336,7 +3336,7 @@
         <v>10</v>
       </c>
       <c r="D267">
-        <v>57</v>
+        <v>121</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -3347,7 +3347,7 @@
         <v>10</v>
       </c>
       <c r="D268">
-        <v>58</v>
+        <v>123</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -3358,7 +3358,7 @@
         <v>10</v>
       </c>
       <c r="D269">
-        <v>59</v>
+        <v>130</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -3369,7 +3369,7 @@
         <v>10</v>
       </c>
       <c r="D270">
-        <v>60</v>
+        <v>138</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -3380,7 +3380,7 @@
         <v>10</v>
       </c>
       <c r="D271">
-        <v>61</v>
+        <v>142</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -3391,7 +3391,7 @@
         <v>10</v>
       </c>
       <c r="D272">
-        <v>64</v>
+        <v>143</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -3402,7 +3402,7 @@
         <v>10</v>
       </c>
       <c r="D273">
-        <v>65</v>
+        <v>145</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -3413,7 +3413,7 @@
         <v>10</v>
       </c>
       <c r="D274">
-        <v>67</v>
+        <v>146</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -3424,7 +3424,7 @@
         <v>10</v>
       </c>
       <c r="D275">
-        <v>68</v>
+        <v>147</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -3435,7 +3435,7 @@
         <v>10</v>
       </c>
       <c r="D276">
-        <v>71</v>
+        <v>149</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -3446,7 +3446,7 @@
         <v>10</v>
       </c>
       <c r="D277">
-        <v>72</v>
+        <v>150</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -3457,7 +3457,7 @@
         <v>10</v>
       </c>
       <c r="D278">
-        <v>74</v>
+        <v>151</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -3468,7 +3468,7 @@
         <v>10</v>
       </c>
       <c r="D279">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -3479,7 +3479,7 @@
         <v>10</v>
       </c>
       <c r="D280">
-        <v>77</v>
+        <v>154</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -3490,7 +3490,7 @@
         <v>10</v>
       </c>
       <c r="D281">
-        <v>78</v>
+        <v>155</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="D282">
-        <v>79</v>
+        <v>156</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -3512,7 +3512,7 @@
         <v>10</v>
       </c>
       <c r="D283">
-        <v>80</v>
+        <v>157</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -3523,7 +3523,7 @@
         <v>10</v>
       </c>
       <c r="D284">
-        <v>81</v>
+        <v>158</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -3534,7 +3534,7 @@
         <v>10</v>
       </c>
       <c r="D285">
-        <v>82</v>
+        <v>161</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -3545,7 +3545,7 @@
         <v>10</v>
       </c>
       <c r="D286">
-        <v>83</v>
+        <v>162</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -3556,7 +3556,7 @@
         <v>10</v>
       </c>
       <c r="D287">
-        <v>84</v>
+        <v>163</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -3567,7 +3567,7 @@
         <v>10</v>
       </c>
       <c r="D288">
-        <v>90</v>
+        <v>167</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -3578,7 +3578,7 @@
         <v>10</v>
       </c>
       <c r="D289">
-        <v>91</v>
+        <v>169</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -3589,7 +3589,7 @@
         <v>10</v>
       </c>
       <c r="D290">
-        <v>92</v>
+        <v>170</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -3600,7 +3600,7 @@
         <v>10</v>
       </c>
       <c r="D291">
-        <v>93</v>
+        <v>171</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -3611,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="D292">
-        <v>94</v>
+        <v>172</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -3622,7 +3622,7 @@
         <v>10</v>
       </c>
       <c r="D293">
-        <v>95</v>
+        <v>174</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -3633,7 +3633,7 @@
         <v>10</v>
       </c>
       <c r="D294">
-        <v>96</v>
+        <v>175</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -3644,7 +3644,7 @@
         <v>10</v>
       </c>
       <c r="D295">
-        <v>97</v>
+        <v>176</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -3655,7 +3655,7 @@
         <v>10</v>
       </c>
       <c r="D296">
-        <v>99</v>
+        <v>177</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -3666,7 +3666,7 @@
         <v>10</v>
       </c>
       <c r="D297">
-        <v>100</v>
+        <v>178</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -3677,7 +3677,7 @@
         <v>10</v>
       </c>
       <c r="D298">
-        <v>104</v>
+        <v>181</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -3688,7 +3688,7 @@
         <v>10</v>
       </c>
       <c r="D299">
-        <v>109</v>
+        <v>182</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -3699,7 +3699,7 @@
         <v>10</v>
       </c>
       <c r="D300">
-        <v>111</v>
+        <v>183</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>10</v>
       </c>
       <c r="D301">
-        <v>112</v>
+        <v>184</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -3721,7 +3721,7 @@
         <v>10</v>
       </c>
       <c r="D302">
-        <v>114</v>
+        <v>185</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -3732,7 +3732,7 @@
         <v>10</v>
       </c>
       <c r="D303">
-        <v>115</v>
+        <v>186</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -3743,7 +3743,7 @@
         <v>10</v>
       </c>
       <c r="D304">
-        <v>116</v>
+        <v>187</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -3754,7 +3754,7 @@
         <v>10</v>
       </c>
       <c r="D305">
-        <v>117</v>
+        <v>188</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -3765,7 +3765,7 @@
         <v>10</v>
       </c>
       <c r="D306">
-        <v>118</v>
+        <v>189</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -3776,7 +3776,7 @@
         <v>10</v>
       </c>
       <c r="D307">
-        <v>119</v>
+        <v>191</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -3787,7 +3787,7 @@
         <v>10</v>
       </c>
       <c r="D308">
-        <v>120</v>
+        <v>192</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -3798,7 +3798,7 @@
         <v>10</v>
       </c>
       <c r="D309">
-        <v>121</v>
+        <v>193</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -3809,7 +3809,7 @@
         <v>10</v>
       </c>
       <c r="D310">
-        <v>123</v>
+        <v>194</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -3820,7 +3820,7 @@
         <v>10</v>
       </c>
       <c r="D311">
-        <v>130</v>
+        <v>198</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -3831,7 +3831,7 @@
         <v>10</v>
       </c>
       <c r="D312">
-        <v>138</v>
+        <v>199</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -3842,7 +3842,7 @@
         <v>10</v>
       </c>
       <c r="D313">
-        <v>142</v>
+        <v>200</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -3853,7 +3853,7 @@
         <v>10</v>
       </c>
       <c r="D314">
-        <v>143</v>
+        <v>201</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -3864,7 +3864,7 @@
         <v>10</v>
       </c>
       <c r="D315">
-        <v>145</v>
+        <v>202</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -3875,7 +3875,7 @@
         <v>10</v>
       </c>
       <c r="D316">
-        <v>146</v>
+        <v>203</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -3886,7 +3886,7 @@
         <v>10</v>
       </c>
       <c r="D317">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -3897,7 +3897,7 @@
         <v>10</v>
       </c>
       <c r="D318">
-        <v>149</v>
+        <v>205</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -3908,7 +3908,7 @@
         <v>10</v>
       </c>
       <c r="D319">
-        <v>150</v>
+        <v>206</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -3919,84 +3919,105 @@
         <v>10</v>
       </c>
       <c r="D320">
-        <v>151</v>
+        <v>207</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B321" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C321" t="s">
+        <v>15</v>
       </c>
       <c r="D321">
-        <v>153</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B322" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C322" t="s">
+        <v>15</v>
       </c>
       <c r="D322">
-        <v>154</v>
+        <v>22</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B323" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C323" t="s">
+        <v>15</v>
       </c>
       <c r="D323">
-        <v>155</v>
+        <v>28</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B324" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C324" t="s">
+        <v>15</v>
       </c>
       <c r="D324">
-        <v>156</v>
+        <v>29</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B325" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C325" t="s">
+        <v>15</v>
       </c>
       <c r="D325">
-        <v>157</v>
+        <v>30</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B326" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C326" t="s">
+        <v>15</v>
       </c>
       <c r="D326">
-        <v>158</v>
+        <v>31</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B327" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C327" t="s">
+        <v>15</v>
       </c>
       <c r="D327">
-        <v>160</v>
+        <v>32</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -4004,10 +4025,10 @@
         <v>5</v>
       </c>
       <c r="B328" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D328">
-        <v>161</v>
+        <v>33</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -4015,43 +4036,52 @@
         <v>5</v>
       </c>
       <c r="B329" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D329">
-        <v>162</v>
+        <v>35</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B330" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C330" t="s">
+        <v>15</v>
       </c>
       <c r="D330">
-        <v>163</v>
+        <v>36</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B331" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C331" t="s">
+        <v>15</v>
       </c>
       <c r="D331">
-        <v>167</v>
+        <v>37</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B332" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C332" t="s">
+        <v>15</v>
       </c>
       <c r="D332">
-        <v>169</v>
+        <v>38</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -4059,21 +4089,24 @@
         <v>5</v>
       </c>
       <c r="B333" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D333">
-        <v>170</v>
+        <v>39</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B334" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C334" t="s">
+        <v>15</v>
       </c>
       <c r="D334">
-        <v>171</v>
+        <v>40</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -4084,7 +4117,7 @@
         <v>10</v>
       </c>
       <c r="D335">
-        <v>172</v>
+        <v>42</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -4095,18 +4128,21 @@
         <v>10</v>
       </c>
       <c r="D336">
-        <v>173</v>
+        <v>43</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B337" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C337" t="s">
+        <v>15</v>
       </c>
       <c r="D337">
-        <v>174</v>
+        <v>44</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -4117,29 +4153,35 @@
         <v>10</v>
       </c>
       <c r="D338">
-        <v>175</v>
+        <v>45</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B339" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C339" t="s">
+        <v>15</v>
       </c>
       <c r="D339">
-        <v>176</v>
+        <v>46</v>
       </c>
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B340" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C340" t="s">
+        <v>15</v>
       </c>
       <c r="D340">
-        <v>177</v>
+        <v>47</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -4150,7 +4192,7 @@
         <v>10</v>
       </c>
       <c r="D341">
-        <v>178</v>
+        <v>48</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -4161,7 +4203,7 @@
         <v>10</v>
       </c>
       <c r="D342">
-        <v>181</v>
+        <v>49</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -4172,7 +4214,7 @@
         <v>10</v>
       </c>
       <c r="D343">
-        <v>182</v>
+        <v>50</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -4183,18 +4225,21 @@
         <v>10</v>
       </c>
       <c r="D344">
-        <v>183</v>
+        <v>51</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B345" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C345" t="s">
+        <v>15</v>
       </c>
       <c r="D345">
-        <v>184</v>
+        <v>52</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -4205,7 +4250,7 @@
         <v>10</v>
       </c>
       <c r="D346">
-        <v>185</v>
+        <v>53</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -4216,29 +4261,35 @@
         <v>10</v>
       </c>
       <c r="D347">
-        <v>186</v>
+        <v>54</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B348" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C348" t="s">
+        <v>15</v>
       </c>
       <c r="D348">
-        <v>187</v>
+        <v>55</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B349" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C349" t="s">
+        <v>15</v>
       </c>
       <c r="D349">
-        <v>188</v>
+        <v>56</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -4249,7 +4300,7 @@
         <v>10</v>
       </c>
       <c r="D350">
-        <v>189</v>
+        <v>57</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -4260,7 +4311,7 @@
         <v>10</v>
       </c>
       <c r="D351">
-        <v>191</v>
+        <v>58</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -4271,7 +4322,7 @@
         <v>10</v>
       </c>
       <c r="D352">
-        <v>192</v>
+        <v>59</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -4282,7 +4333,7 @@
         <v>10</v>
       </c>
       <c r="D353">
-        <v>193</v>
+        <v>60</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -4293,29 +4344,35 @@
         <v>10</v>
       </c>
       <c r="D354">
-        <v>194</v>
+        <v>61</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B355" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C355" t="s">
+        <v>15</v>
       </c>
       <c r="D355">
-        <v>198</v>
+        <v>62</v>
       </c>
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B356" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C356" t="s">
+        <v>15</v>
       </c>
       <c r="D356">
-        <v>199</v>
+        <v>63</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -4326,7 +4383,7 @@
         <v>10</v>
       </c>
       <c r="D357">
-        <v>200</v>
+        <v>64</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -4337,18 +4394,21 @@
         <v>10</v>
       </c>
       <c r="D358">
-        <v>201</v>
+        <v>65</v>
       </c>
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B359" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C359" t="s">
+        <v>15</v>
       </c>
       <c r="D359">
-        <v>202</v>
+        <v>66</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -4359,7 +4419,7 @@
         <v>10</v>
       </c>
       <c r="D360">
-        <v>203</v>
+        <v>67</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -4370,29 +4430,35 @@
         <v>10</v>
       </c>
       <c r="D361">
-        <v>204</v>
+        <v>68</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B362" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C362" t="s">
+        <v>15</v>
       </c>
       <c r="D362">
-        <v>205</v>
+        <v>69</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B363" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C363" t="s">
+        <v>15</v>
       </c>
       <c r="D363">
-        <v>206</v>
+        <v>70</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -4403,21 +4469,18 @@
         <v>10</v>
       </c>
       <c r="D364">
-        <v>207</v>
+        <v>71</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B365" t="s">
-        <v>11</v>
-      </c>
-      <c r="C365" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D365">
-        <v>3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -4431,77 +4494,62 @@
         <v>15</v>
       </c>
       <c r="D366">
-        <v>22</v>
+        <v>73</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B367" t="s">
-        <v>11</v>
-      </c>
-      <c r="C367" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D367">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B368" t="s">
-        <v>11</v>
-      </c>
-      <c r="C368" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D368">
-        <v>29</v>
+        <v>75</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B369" t="s">
-        <v>11</v>
-      </c>
-      <c r="C369" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D369">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B370" t="s">
-        <v>11</v>
-      </c>
-      <c r="C370" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D370">
-        <v>31</v>
+        <v>78</v>
       </c>
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B371" t="s">
-        <v>11</v>
-      </c>
-      <c r="C371" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D371">
-        <v>32</v>
+        <v>79</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -4509,24 +4557,21 @@
         <v>5</v>
       </c>
       <c r="B372" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D372">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B373" t="s">
-        <v>11</v>
-      </c>
-      <c r="C373" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D373">
-        <v>34</v>
+        <v>81</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -4534,10 +4579,10 @@
         <v>5</v>
       </c>
       <c r="B374" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D374">
-        <v>35</v>
+        <v>82</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -4551,7 +4596,7 @@
         <v>15</v>
       </c>
       <c r="D375">
-        <v>36</v>
+        <v>85</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -4565,7 +4610,7 @@
         <v>15</v>
       </c>
       <c r="D376">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -4579,18 +4624,21 @@
         <v>15</v>
       </c>
       <c r="D377">
-        <v>38</v>
+        <v>87</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B378" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="C378" t="s">
+        <v>15</v>
       </c>
       <c r="D378">
-        <v>39</v>
+        <v>88</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -4604,18 +4652,21 @@
         <v>15</v>
       </c>
       <c r="D379">
-        <v>40</v>
+        <v>89</v>
       </c>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B380" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C380" t="s">
+        <v>15</v>
       </c>
       <c r="D380">
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -4623,63 +4674,57 @@
         <v>5</v>
       </c>
       <c r="B381" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D381">
-        <v>43</v>
+        <v>91</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B382" t="s">
-        <v>11</v>
-      </c>
-      <c r="C382" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D382">
-        <v>44</v>
+        <v>93</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B383" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C383" t="s">
+        <v>15</v>
       </c>
       <c r="D383">
-        <v>45</v>
+        <v>94</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B384" t="s">
-        <v>11</v>
-      </c>
-      <c r="C384" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D384">
-        <v>46</v>
+        <v>95</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B385" t="s">
-        <v>11</v>
-      </c>
-      <c r="C385" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D385">
-        <v>47</v>
+        <v>96</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -4690,18 +4735,21 @@
         <v>10</v>
       </c>
       <c r="D386">
-        <v>48</v>
+        <v>97</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B387" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C387" t="s">
+        <v>15</v>
       </c>
       <c r="D387">
-        <v>49</v>
+        <v>98</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -4712,7 +4760,7 @@
         <v>10</v>
       </c>
       <c r="D388">
-        <v>50</v>
+        <v>99</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -4723,7 +4771,7 @@
         <v>10</v>
       </c>
       <c r="D389">
-        <v>51</v>
+        <v>100</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -4737,29 +4785,35 @@
         <v>15</v>
       </c>
       <c r="D390">
-        <v>52</v>
+        <v>101</v>
       </c>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B391" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C391" t="s">
+        <v>15</v>
       </c>
       <c r="D391">
-        <v>53</v>
+        <v>103</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B392" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C392" t="s">
+        <v>15</v>
       </c>
       <c r="D392">
-        <v>54</v>
+        <v>104</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -4773,7 +4827,7 @@
         <v>15</v>
       </c>
       <c r="D393">
-        <v>55</v>
+        <v>105</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -4787,29 +4841,35 @@
         <v>15</v>
       </c>
       <c r="D394">
-        <v>56</v>
+        <v>106</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B395" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C395" t="s">
+        <v>15</v>
       </c>
       <c r="D395">
-        <v>57</v>
+        <v>107</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B396" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C396" t="s">
+        <v>15</v>
       </c>
       <c r="D396">
-        <v>58</v>
+        <v>108</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -4820,18 +4880,21 @@
         <v>10</v>
       </c>
       <c r="D397">
-        <v>59</v>
+        <v>109</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B398" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C398" t="s">
+        <v>15</v>
       </c>
       <c r="D398">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -4842,21 +4905,18 @@
         <v>10</v>
       </c>
       <c r="D399">
-        <v>61</v>
+        <v>111</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B400" t="s">
-        <v>11</v>
-      </c>
-      <c r="C400" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D400">
-        <v>62</v>
+        <v>112</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -4870,18 +4930,21 @@
         <v>15</v>
       </c>
       <c r="D401">
-        <v>63</v>
+        <v>113</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B402" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C402" t="s">
+        <v>15</v>
       </c>
       <c r="D402">
-        <v>64</v>
+        <v>114</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -4892,21 +4955,18 @@
         <v>10</v>
       </c>
       <c r="D403">
-        <v>65</v>
+        <v>115</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B404" t="s">
-        <v>11</v>
-      </c>
-      <c r="C404" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D404">
-        <v>66</v>
+        <v>116</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -4917,7 +4977,7 @@
         <v>10</v>
       </c>
       <c r="D405">
-        <v>67</v>
+        <v>117</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -4928,7 +4988,7 @@
         <v>10</v>
       </c>
       <c r="D406">
-        <v>68</v>
+        <v>121</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -4942,21 +5002,18 @@
         <v>15</v>
       </c>
       <c r="D407">
-        <v>69</v>
+        <v>122</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B408" t="s">
-        <v>11</v>
-      </c>
-      <c r="C408" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D408">
-        <v>70</v>
+        <v>123</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -4970,18 +5027,21 @@
         <v>15</v>
       </c>
       <c r="D409">
-        <v>71</v>
+        <v>124</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B410" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C410" t="s">
+        <v>15</v>
       </c>
       <c r="D410">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -4995,73 +5055,91 @@
         <v>15</v>
       </c>
       <c r="D411">
-        <v>73</v>
+        <v>126</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B412" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C412" t="s">
+        <v>15</v>
       </c>
       <c r="D412">
-        <v>74</v>
+        <v>127</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B413" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C413" t="s">
+        <v>15</v>
       </c>
       <c r="D413">
-        <v>75</v>
+        <v>128</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B414" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C414" t="s">
+        <v>15</v>
       </c>
       <c r="D414">
-        <v>77</v>
+        <v>129</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B415" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C415" t="s">
+        <v>15</v>
       </c>
       <c r="D415">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B416" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C416" t="s">
+        <v>15</v>
       </c>
       <c r="D416">
-        <v>79</v>
+        <v>137</v>
       </c>
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B417" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C417" t="s">
+        <v>15</v>
       </c>
       <c r="D417">
-        <v>80</v>
+        <v>141</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -5072,7 +5150,7 @@
         <v>10</v>
       </c>
       <c r="D418">
-        <v>81</v>
+        <v>142</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -5083,91 +5161,73 @@
         <v>10</v>
       </c>
       <c r="D419">
-        <v>82</v>
+        <v>143</v>
       </c>
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B420" t="s">
-        <v>11</v>
-      </c>
-      <c r="C420" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D420">
-        <v>85</v>
+        <v>145</v>
       </c>
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B421" t="s">
-        <v>11</v>
-      </c>
-      <c r="C421" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D421">
-        <v>86</v>
+        <v>146</v>
       </c>
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B422" t="s">
-        <v>11</v>
-      </c>
-      <c r="C422" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D422">
-        <v>87</v>
+        <v>147</v>
       </c>
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B423" t="s">
-        <v>11</v>
-      </c>
-      <c r="C423" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D423">
-        <v>88</v>
+        <v>149</v>
       </c>
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B424" t="s">
-        <v>11</v>
-      </c>
-      <c r="C424" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D424">
-        <v>89</v>
+        <v>151</v>
       </c>
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B425" t="s">
-        <v>11</v>
-      </c>
-      <c r="C425" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D425">
-        <v>90</v>
+        <v>154</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -5178,7 +5238,7 @@
         <v>10</v>
       </c>
       <c r="D426">
-        <v>91</v>
+        <v>155</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -5189,21 +5249,18 @@
         <v>10</v>
       </c>
       <c r="D427">
-        <v>93</v>
+        <v>156</v>
       </c>
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B428" t="s">
-        <v>11</v>
-      </c>
-      <c r="C428" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D428">
-        <v>94</v>
+        <v>157</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -5214,43 +5271,46 @@
         <v>10</v>
       </c>
       <c r="D429">
-        <v>95</v>
+        <v>158</v>
       </c>
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B430" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C430" t="s">
+        <v>15</v>
       </c>
       <c r="D430">
-        <v>96</v>
+        <v>159</v>
       </c>
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B431" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C431" t="s">
+        <v>15</v>
       </c>
       <c r="D431">
-        <v>97</v>
+        <v>160</v>
       </c>
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B432" t="s">
-        <v>11</v>
-      </c>
-      <c r="C432" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D432">
-        <v>98</v>
+        <v>161</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -5261,7 +5321,7 @@
         <v>10</v>
       </c>
       <c r="D433">
-        <v>99</v>
+        <v>162</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -5272,7 +5332,7 @@
         <v>10</v>
       </c>
       <c r="D434">
-        <v>100</v>
+        <v>163</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -5286,7 +5346,7 @@
         <v>15</v>
       </c>
       <c r="D435">
-        <v>101</v>
+        <v>165</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -5300,7 +5360,7 @@
         <v>15</v>
       </c>
       <c r="D436">
-        <v>103</v>
+        <v>166</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -5314,88 +5374,76 @@
         <v>15</v>
       </c>
       <c r="D437">
-        <v>104</v>
+        <v>168</v>
       </c>
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B438" t="s">
-        <v>11</v>
-      </c>
-      <c r="C438" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D438">
-        <v>105</v>
+        <v>169</v>
       </c>
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B439" t="s">
-        <v>11</v>
-      </c>
-      <c r="C439" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D439">
-        <v>106</v>
+        <v>170</v>
       </c>
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B440" t="s">
-        <v>11</v>
-      </c>
-      <c r="C440" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D440">
-        <v>107</v>
+        <v>171</v>
       </c>
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B441" t="s">
-        <v>11</v>
-      </c>
-      <c r="C441" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D441">
-        <v>108</v>
+        <v>172</v>
       </c>
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B442" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C442" t="s">
+        <v>15</v>
       </c>
       <c r="D442">
-        <v>109</v>
+        <v>173</v>
       </c>
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B443" t="s">
-        <v>11</v>
-      </c>
-      <c r="C443" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D443">
-        <v>110</v>
+        <v>176</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -5406,7 +5454,7 @@
         <v>10</v>
       </c>
       <c r="D444">
-        <v>111</v>
+        <v>177</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -5417,7 +5465,7 @@
         <v>10</v>
       </c>
       <c r="D445">
-        <v>112</v>
+        <v>178</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -5431,7 +5479,7 @@
         <v>15</v>
       </c>
       <c r="D446">
-        <v>113</v>
+        <v>179</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -5445,7 +5493,7 @@
         <v>15</v>
       </c>
       <c r="D447">
-        <v>114</v>
+        <v>180</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -5456,7 +5504,7 @@
         <v>10</v>
       </c>
       <c r="D448">
-        <v>115</v>
+        <v>181</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -5467,7 +5515,7 @@
         <v>10</v>
       </c>
       <c r="D449">
-        <v>116</v>
+        <v>182</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -5478,7 +5526,7 @@
         <v>10</v>
       </c>
       <c r="D450">
-        <v>117</v>
+        <v>185</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -5489,21 +5537,18 @@
         <v>10</v>
       </c>
       <c r="D451">
-        <v>121</v>
+        <v>186</v>
       </c>
     </row>
     <row r="452" spans="1:4">
       <c r="A452" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B452" t="s">
-        <v>11</v>
-      </c>
-      <c r="C452" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D452">
-        <v>122</v>
+        <v>187</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -5514,7 +5559,7 @@
         <v>10</v>
       </c>
       <c r="D453">
-        <v>123</v>
+        <v>189</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -5528,49 +5573,40 @@
         <v>15</v>
       </c>
       <c r="D454">
-        <v>124</v>
+        <v>190</v>
       </c>
     </row>
     <row r="455" spans="1:4">
       <c r="A455" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B455" t="s">
-        <v>11</v>
-      </c>
-      <c r="C455" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D455">
-        <v>125</v>
+        <v>191</v>
       </c>
     </row>
     <row r="456" spans="1:4">
       <c r="A456" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B456" t="s">
-        <v>11</v>
-      </c>
-      <c r="C456" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D456">
-        <v>126</v>
+        <v>192</v>
       </c>
     </row>
     <row r="457" spans="1:4">
       <c r="A457" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B457" t="s">
-        <v>11</v>
-      </c>
-      <c r="C457" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D457">
-        <v>127</v>
+        <v>194</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -5584,7 +5620,7 @@
         <v>15</v>
       </c>
       <c r="D458">
-        <v>128</v>
+        <v>195</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -5598,7 +5634,7 @@
         <v>15</v>
       </c>
       <c r="D459">
-        <v>129</v>
+        <v>196</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -5612,35 +5648,29 @@
         <v>15</v>
       </c>
       <c r="D460">
-        <v>133</v>
+        <v>197</v>
       </c>
     </row>
     <row r="461" spans="1:4">
       <c r="A461" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B461" t="s">
-        <v>11</v>
-      </c>
-      <c r="C461" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D461">
-        <v>137</v>
+        <v>198</v>
       </c>
     </row>
     <row r="462" spans="1:4">
       <c r="A462" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B462" t="s">
-        <v>11</v>
-      </c>
-      <c r="C462" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D462">
-        <v>141</v>
+        <v>200</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -5651,7 +5681,7 @@
         <v>10</v>
       </c>
       <c r="D463">
-        <v>142</v>
+        <v>202</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -5662,7 +5692,7 @@
         <v>10</v>
       </c>
       <c r="D464">
-        <v>143</v>
+        <v>203</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -5673,7 +5703,7 @@
         <v>10</v>
       </c>
       <c r="D465">
-        <v>145</v>
+        <v>204</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -5684,7 +5714,7 @@
         <v>10</v>
       </c>
       <c r="D466">
-        <v>146</v>
+        <v>205</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -5695,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="D467">
-        <v>147</v>
+        <v>206</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -5706,562 +5736,22 @@
         <v>10</v>
       </c>
       <c r="D468">
-        <v>149</v>
+        <v>207</v>
       </c>
     </row>
     <row r="469" spans="1:4">
       <c r="A469" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B469" t="s">
-        <v>10</v>
-      </c>
-      <c r="D469">
-        <v>151</v>
+        <v>12</v>
       </c>
     </row>
     <row r="470" spans="1:4">
       <c r="A470" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B470" t="s">
-        <v>11</v>
-      </c>
-      <c r="C470" t="s">
-        <v>15</v>
-      </c>
-      <c r="D470">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="471" spans="1:4">
-      <c r="A471" t="s">
-        <v>5</v>
-      </c>
-      <c r="B471" t="s">
-        <v>10</v>
-      </c>
-      <c r="D471">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="472" spans="1:4">
-      <c r="A472" t="s">
-        <v>6</v>
-      </c>
-      <c r="B472" t="s">
-        <v>11</v>
-      </c>
-      <c r="C472" t="s">
-        <v>15</v>
-      </c>
-      <c r="D472">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="473" spans="1:4">
-      <c r="A473" t="s">
-        <v>5</v>
-      </c>
-      <c r="B473" t="s">
-        <v>10</v>
-      </c>
-      <c r="D473">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="474" spans="1:4">
-      <c r="A474" t="s">
-        <v>6</v>
-      </c>
-      <c r="B474" t="s">
-        <v>11</v>
-      </c>
-      <c r="C474" t="s">
-        <v>15</v>
-      </c>
-      <c r="D474">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="475" spans="1:4">
-      <c r="A475" t="s">
-        <v>6</v>
-      </c>
-      <c r="B475" t="s">
-        <v>11</v>
-      </c>
-      <c r="C475" t="s">
-        <v>15</v>
-      </c>
-      <c r="D475">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="476" spans="1:4">
-      <c r="A476" t="s">
-        <v>6</v>
-      </c>
-      <c r="B476" t="s">
-        <v>11</v>
-      </c>
-      <c r="C476" t="s">
-        <v>15</v>
-      </c>
-      <c r="D476">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="477" spans="1:4">
-      <c r="A477" t="s">
-        <v>5</v>
-      </c>
-      <c r="B477" t="s">
-        <v>10</v>
-      </c>
-      <c r="D477">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="478" spans="1:4">
-      <c r="A478" t="s">
-        <v>5</v>
-      </c>
-      <c r="B478" t="s">
-        <v>10</v>
-      </c>
-      <c r="D478">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="479" spans="1:4">
-      <c r="A479" t="s">
-        <v>5</v>
-      </c>
-      <c r="B479" t="s">
-        <v>10</v>
-      </c>
-      <c r="D479">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="480" spans="1:4">
-      <c r="A480" t="s">
-        <v>6</v>
-      </c>
-      <c r="B480" t="s">
-        <v>11</v>
-      </c>
-      <c r="C480" t="s">
-        <v>15</v>
-      </c>
-      <c r="D480">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="481" spans="1:4">
-      <c r="A481" t="s">
-        <v>6</v>
-      </c>
-      <c r="B481" t="s">
-        <v>11</v>
-      </c>
-      <c r="C481" t="s">
-        <v>15</v>
-      </c>
-      <c r="D481">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="482" spans="1:4">
-      <c r="A482" t="s">
-        <v>6</v>
-      </c>
-      <c r="B482" t="s">
-        <v>11</v>
-      </c>
-      <c r="C482" t="s">
-        <v>15</v>
-      </c>
-      <c r="D482">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="483" spans="1:4">
-      <c r="A483" t="s">
-        <v>5</v>
-      </c>
-      <c r="B483" t="s">
-        <v>10</v>
-      </c>
-      <c r="D483">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="484" spans="1:4">
-      <c r="A484" t="s">
-        <v>5</v>
-      </c>
-      <c r="B484" t="s">
-        <v>10</v>
-      </c>
-      <c r="D484">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="485" spans="1:4">
-      <c r="A485" t="s">
-        <v>5</v>
-      </c>
-      <c r="B485" t="s">
-        <v>10</v>
-      </c>
-      <c r="D485">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="486" spans="1:4">
-      <c r="A486" t="s">
-        <v>5</v>
-      </c>
-      <c r="B486" t="s">
-        <v>10</v>
-      </c>
-      <c r="D486">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="487" spans="1:4">
-      <c r="A487" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" t="s">
-        <v>11</v>
-      </c>
-      <c r="C487" t="s">
-        <v>15</v>
-      </c>
-      <c r="D487">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="488" spans="1:4">
-      <c r="A488" t="s">
-        <v>5</v>
-      </c>
-      <c r="B488" t="s">
-        <v>10</v>
-      </c>
-      <c r="D488">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="489" spans="1:4">
-      <c r="A489" t="s">
-        <v>5</v>
-      </c>
-      <c r="B489" t="s">
-        <v>10</v>
-      </c>
-      <c r="D489">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="490" spans="1:4">
-      <c r="A490" t="s">
-        <v>5</v>
-      </c>
-      <c r="B490" t="s">
-        <v>10</v>
-      </c>
-      <c r="D490">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="491" spans="1:4">
-      <c r="A491" t="s">
-        <v>6</v>
-      </c>
-      <c r="B491" t="s">
-        <v>11</v>
-      </c>
-      <c r="C491" t="s">
-        <v>15</v>
-      </c>
-      <c r="D491">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="492" spans="1:4">
-      <c r="A492" t="s">
-        <v>6</v>
-      </c>
-      <c r="B492" t="s">
-        <v>11</v>
-      </c>
-      <c r="C492" t="s">
-        <v>15</v>
-      </c>
-      <c r="D492">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="493" spans="1:4">
-      <c r="A493" t="s">
-        <v>5</v>
-      </c>
-      <c r="B493" t="s">
-        <v>10</v>
-      </c>
-      <c r="D493">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="494" spans="1:4">
-      <c r="A494" t="s">
-        <v>5</v>
-      </c>
-      <c r="B494" t="s">
-        <v>10</v>
-      </c>
-      <c r="D494">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="495" spans="1:4">
-      <c r="A495" t="s">
-        <v>5</v>
-      </c>
-      <c r="B495" t="s">
-        <v>10</v>
-      </c>
-      <c r="D495">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="496" spans="1:4">
-      <c r="A496" t="s">
-        <v>5</v>
-      </c>
-      <c r="B496" t="s">
-        <v>10</v>
-      </c>
-      <c r="D496">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="497" spans="1:4">
-      <c r="A497" t="s">
-        <v>5</v>
-      </c>
-      <c r="B497" t="s">
-        <v>10</v>
-      </c>
-      <c r="D497">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="498" spans="1:4">
-      <c r="A498" t="s">
-        <v>5</v>
-      </c>
-      <c r="B498" t="s">
-        <v>10</v>
-      </c>
-      <c r="D498">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="499" spans="1:4">
-      <c r="A499" t="s">
-        <v>6</v>
-      </c>
-      <c r="B499" t="s">
-        <v>11</v>
-      </c>
-      <c r="C499" t="s">
-        <v>15</v>
-      </c>
-      <c r="D499">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="500" spans="1:4">
-      <c r="A500" t="s">
-        <v>5</v>
-      </c>
-      <c r="B500" t="s">
-        <v>10</v>
-      </c>
-      <c r="D500">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="501" spans="1:4">
-      <c r="A501" t="s">
-        <v>5</v>
-      </c>
-      <c r="B501" t="s">
-        <v>10</v>
-      </c>
-      <c r="D501">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="502" spans="1:4">
-      <c r="A502" t="s">
-        <v>5</v>
-      </c>
-      <c r="B502" t="s">
-        <v>10</v>
-      </c>
-      <c r="D502">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="503" spans="1:4">
-      <c r="A503" t="s">
-        <v>6</v>
-      </c>
-      <c r="B503" t="s">
-        <v>11</v>
-      </c>
-      <c r="C503" t="s">
-        <v>15</v>
-      </c>
-      <c r="D503">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="504" spans="1:4">
-      <c r="A504" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" t="s">
-        <v>11</v>
-      </c>
-      <c r="C504" t="s">
-        <v>15</v>
-      </c>
-      <c r="D504">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="505" spans="1:4">
-      <c r="A505" t="s">
-        <v>6</v>
-      </c>
-      <c r="B505" t="s">
-        <v>11</v>
-      </c>
-      <c r="C505" t="s">
-        <v>15</v>
-      </c>
-      <c r="D505">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="506" spans="1:4">
-      <c r="A506" t="s">
-        <v>5</v>
-      </c>
-      <c r="B506" t="s">
-        <v>10</v>
-      </c>
-      <c r="D506">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="507" spans="1:4">
-      <c r="A507" t="s">
-        <v>5</v>
-      </c>
-      <c r="B507" t="s">
-        <v>10</v>
-      </c>
-      <c r="D507">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="508" spans="1:4">
-      <c r="A508" t="s">
-        <v>5</v>
-      </c>
-      <c r="B508" t="s">
-        <v>10</v>
-      </c>
-      <c r="D508">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="509" spans="1:4">
-      <c r="A509" t="s">
-        <v>5</v>
-      </c>
-      <c r="B509" t="s">
-        <v>10</v>
-      </c>
-      <c r="D509">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="510" spans="1:4">
-      <c r="A510" t="s">
-        <v>5</v>
-      </c>
-      <c r="B510" t="s">
-        <v>10</v>
-      </c>
-      <c r="D510">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="511" spans="1:4">
-      <c r="A511" t="s">
-        <v>5</v>
-      </c>
-      <c r="B511" t="s">
-        <v>10</v>
-      </c>
-      <c r="D511">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="512" spans="1:4">
-      <c r="A512" t="s">
-        <v>5</v>
-      </c>
-      <c r="B512" t="s">
-        <v>10</v>
-      </c>
-      <c r="D512">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="513" spans="1:4">
-      <c r="A513" t="s">
-        <v>5</v>
-      </c>
-      <c r="B513" t="s">
-        <v>10</v>
-      </c>
-      <c r="D513">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="514" spans="1:4">
-      <c r="A514" t="s">
-        <v>7</v>
-      </c>
-      <c r="B514" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="515" spans="1:4">
-      <c r="A515" t="s">
-        <v>7</v>
-      </c>
-      <c r="B515" t="s">
         <v>13</v>
       </c>
     </row>
